--- a/cashflow_templates/A_月次資金繰り表_25か月_入力中.xlsx
+++ b/cashflow_templates/A_月次資金繰り表_25か月_入力中.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -76,15 +76,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="游ゴシック"/>
       <charset val="128"/>
-      <family val="2"/>
+      <family val="3"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -153,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,26 +180,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -232,6 +222,20 @@
         <b val="1"/>
         <color rgb="FFC00000"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -383,9 +387,9 @@
         <t>初月の本来の納付額。以降は前月と同額が自動で入ります。保険料率・住民税額が変わる月だけ、そのセルに金額を上書きしてください。</t>
       </text>
     </comment>
-    <comment ref="B57" authorId="1" shapeId="0">
+    <comment ref="B64" authorId="1" shapeId="0">
       <text>
-        <t>初月の本来の納付額。以降は前月と同額が自動で入ります。保険料率・住民税額が変わる月だけ、そのセルに金額を上書きしてください。</t>
+        <t>2025年10月初めの借入金残高（全金融機関の合計）を入力。2か月目以降は自動。</t>
       </text>
     </comment>
   </commentList>
@@ -681,14 +685,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B18"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -696,7 +699,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="17" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -774,7 +776,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -793,6 +794,13 @@
       <c r="B18" s="6" t="inlineStr">
         <is>
           <t>残高が「最低必要残高」を下回ると赤く表示されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>■ 借入金残高：下部「借入金残高管理」の B64 に期首の借入金残高を入力。以降は上段の借入金・借入金返済から自動計算されます。</t>
         </is>
       </c>
     </row>
@@ -807,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA69"/>
+  <dimension ref="A1:AA71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -838,7 +846,7 @@
       <c r="B3" s="8" t="n">
         <v>45931</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="27">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -853,7 +861,7 @@
           <t>最低必要残高（円）</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
+      <c r="B4" s="28" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -862,7 +870,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
@@ -981,32 +988,32 @@
           <t>経常収支</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
-      <c r="Q8" s="27" t="n"/>
-      <c r="R8" s="27" t="n"/>
-      <c r="S8" s="27" t="n"/>
-      <c r="T8" s="27" t="n"/>
-      <c r="U8" s="27" t="n"/>
-      <c r="V8" s="27" t="n"/>
-      <c r="W8" s="27" t="n"/>
-      <c r="X8" s="27" t="n"/>
-      <c r="Y8" s="27" t="n"/>
-      <c r="Z8" s="27" t="n"/>
-      <c r="AA8" s="27" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+      <c r="P8" s="29" t="n"/>
+      <c r="Q8" s="29" t="n"/>
+      <c r="R8" s="29" t="n"/>
+      <c r="S8" s="29" t="n"/>
+      <c r="T8" s="29" t="n"/>
+      <c r="U8" s="29" t="n"/>
+      <c r="V8" s="29" t="n"/>
+      <c r="W8" s="29" t="n"/>
+      <c r="X8" s="29" t="n"/>
+      <c r="Y8" s="29" t="n"/>
+      <c r="Z8" s="29" t="n"/>
+      <c r="AA8" s="29" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1014,82 +1021,82 @@
           <t xml:space="preserve">  収入｜営業収入</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="28" t="n">
         <v>11571200</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="28" t="n">
         <v>12729500</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="28" t="n">
         <v>10817650</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="28" t="n">
         <v>7592596</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="28" t="n">
         <v>12008250</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="28" t="n">
         <v>14734304</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="28" t="n">
         <v>14492300</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="28" t="n">
         <v>9738050</v>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J9" s="28" t="n">
         <v>12227100</v>
       </c>
-      <c r="K9" s="26" t="n">
+      <c r="K9" s="28" t="n">
         <v>7979350</v>
       </c>
-      <c r="L9" s="26" t="n">
+      <c r="L9" s="28" t="n">
         <v>13590955</v>
       </c>
-      <c r="M9" s="26" t="n">
+      <c r="M9" s="28" t="n">
         <v>9548770</v>
       </c>
-      <c r="N9" s="26" t="n">
+      <c r="N9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="O9" s="26" t="n">
+      <c r="O9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="P9" s="26" t="n">
+      <c r="P9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="Q9" s="26" t="n">
+      <c r="Q9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="R9" s="26" t="n">
+      <c r="R9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="S9" s="26" t="n">
+      <c r="S9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="T9" s="26" t="n">
+      <c r="T9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="U9" s="26" t="n">
+      <c r="U9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="V9" s="26" t="n">
+      <c r="V9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="W9" s="26" t="n">
+      <c r="W9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="X9" s="26" t="n">
+      <c r="X9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="Y9" s="26" t="n">
+      <c r="Y9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="Z9" s="26" t="n">
+      <c r="Z9" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="AA9" s="28">
+      <c r="AA9" s="30">
         <f>SUM(B9:Z9)</f>
         <v/>
       </c>
@@ -1100,32 +1107,32 @@
           <t xml:space="preserve">  収入｜案件収入</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="26" t="n"/>
-      <c r="L10" s="26" t="n"/>
-      <c r="M10" s="26" t="n"/>
-      <c r="N10" s="26" t="n"/>
-      <c r="O10" s="26" t="n"/>
-      <c r="P10" s="26" t="n"/>
-      <c r="Q10" s="26" t="n"/>
-      <c r="R10" s="26" t="n"/>
-      <c r="S10" s="26" t="n"/>
-      <c r="T10" s="26" t="n"/>
-      <c r="U10" s="26" t="n"/>
-      <c r="V10" s="26" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="26" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28">
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="28" t="n"/>
+      <c r="O10" s="28" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n"/>
+      <c r="R10" s="28" t="n"/>
+      <c r="S10" s="28" t="n"/>
+      <c r="T10" s="28" t="n"/>
+      <c r="U10" s="28" t="n"/>
+      <c r="V10" s="28" t="n"/>
+      <c r="W10" s="28" t="n"/>
+      <c r="X10" s="28" t="n"/>
+      <c r="Y10" s="28" t="n"/>
+      <c r="Z10" s="28" t="n"/>
+      <c r="AA10" s="30">
         <f>SUM(B10:Z10)</f>
         <v/>
       </c>
@@ -1136,32 +1143,32 @@
           <t xml:space="preserve">  収入｜</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="n"/>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="26" t="n"/>
-      <c r="K11" s="26" t="n"/>
-      <c r="L11" s="26" t="n"/>
-      <c r="M11" s="26" t="n"/>
-      <c r="N11" s="26" t="n"/>
-      <c r="O11" s="26" t="n"/>
-      <c r="P11" s="26" t="n"/>
-      <c r="Q11" s="26" t="n"/>
-      <c r="R11" s="26" t="n"/>
-      <c r="S11" s="26" t="n"/>
-      <c r="T11" s="26" t="n"/>
-      <c r="U11" s="26" t="n"/>
-      <c r="V11" s="26" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="26" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28">
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n"/>
+      <c r="R11" s="28" t="n"/>
+      <c r="S11" s="28" t="n"/>
+      <c r="T11" s="28" t="n"/>
+      <c r="U11" s="28" t="n"/>
+      <c r="V11" s="28" t="n"/>
+      <c r="W11" s="28" t="n"/>
+      <c r="X11" s="28" t="n"/>
+      <c r="Y11" s="28" t="n"/>
+      <c r="Z11" s="28" t="n"/>
+      <c r="AA11" s="30">
         <f>SUM(B11:Z11)</f>
         <v/>
       </c>
@@ -1172,32 +1179,32 @@
           <t xml:space="preserve">  収入｜その他収入</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n"/>
-      <c r="P12" s="26" t="n"/>
-      <c r="Q12" s="26" t="n"/>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="26" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="26" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28">
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="28" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n"/>
+      <c r="R12" s="28" t="n"/>
+      <c r="S12" s="28" t="n"/>
+      <c r="T12" s="28" t="n"/>
+      <c r="U12" s="28" t="n"/>
+      <c r="V12" s="28" t="n"/>
+      <c r="W12" s="28" t="n"/>
+      <c r="X12" s="28" t="n"/>
+      <c r="Y12" s="28" t="n"/>
+      <c r="Z12" s="28" t="n"/>
+      <c r="AA12" s="30">
         <f>SUM(B12:Z12)</f>
         <v/>
       </c>
@@ -1208,107 +1215,107 @@
           <t xml:space="preserve">  収入 計</t>
         </is>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="31">
         <f>SUM(B9:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="31">
         <f>SUM(C9:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="31">
         <f>SUM(D9:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="31">
         <f>SUM(E9:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="31">
         <f>SUM(F9:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="31">
         <f>SUM(G9:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="31">
         <f>SUM(H9:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="31">
         <f>SUM(I9:I12)</f>
         <v/>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="31">
         <f>SUM(J9:J12)</f>
         <v/>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="31">
         <f>SUM(K9:K12)</f>
         <v/>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="31">
         <f>SUM(L9:L12)</f>
         <v/>
       </c>
-      <c r="M13" s="29">
+      <c r="M13" s="31">
         <f>SUM(M9:M12)</f>
         <v/>
       </c>
-      <c r="N13" s="29">
+      <c r="N13" s="31">
         <f>SUM(N9:N12)</f>
         <v/>
       </c>
-      <c r="O13" s="29">
+      <c r="O13" s="31">
         <f>SUM(O9:O12)</f>
         <v/>
       </c>
-      <c r="P13" s="29">
+      <c r="P13" s="31">
         <f>SUM(P9:P12)</f>
         <v/>
       </c>
-      <c r="Q13" s="29">
+      <c r="Q13" s="31">
         <f>SUM(Q9:Q12)</f>
         <v/>
       </c>
-      <c r="R13" s="29">
+      <c r="R13" s="31">
         <f>SUM(R9:R12)</f>
         <v/>
       </c>
-      <c r="S13" s="29">
+      <c r="S13" s="31">
         <f>SUM(S9:S12)</f>
         <v/>
       </c>
-      <c r="T13" s="29">
+      <c r="T13" s="31">
         <f>SUM(T9:T12)</f>
         <v/>
       </c>
-      <c r="U13" s="29">
+      <c r="U13" s="31">
         <f>SUM(U9:U12)</f>
         <v/>
       </c>
-      <c r="V13" s="29">
+      <c r="V13" s="31">
         <f>SUM(V9:V12)</f>
         <v/>
       </c>
-      <c r="W13" s="29">
+      <c r="W13" s="31">
         <f>SUM(W9:W12)</f>
         <v/>
       </c>
-      <c r="X13" s="29">
+      <c r="X13" s="31">
         <f>SUM(X9:X12)</f>
         <v/>
       </c>
-      <c r="Y13" s="29">
+      <c r="Y13" s="31">
         <f>SUM(Y9:Y12)</f>
         <v/>
       </c>
-      <c r="Z13" s="29">
+      <c r="Z13" s="31">
         <f>SUM(Z9:Z12)</f>
         <v/>
       </c>
-      <c r="AA13" s="29">
+      <c r="AA13" s="31">
         <f>SUM(AA9:AA12)</f>
         <v/>
       </c>
@@ -1319,56 +1326,82 @@
           <t xml:space="preserve">  支出｜外注費支払</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="M14" s="26" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="N14" s="26" t="n"/>
-      <c r="O14" s="26" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="26" t="n"/>
-      <c r="R14" s="26" t="n"/>
-      <c r="S14" s="26" t="n"/>
-      <c r="T14" s="26" t="n"/>
-      <c r="U14" s="26" t="n"/>
-      <c r="V14" s="26" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="26" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28">
+      <c r="B14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="L14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="M14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="P14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Q14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="R14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="S14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="T14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="U14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="V14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="W14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="X14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Y14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Z14" s="28" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AA14" s="30">
         <f>SUM(B14:Z14)</f>
         <v/>
       </c>
@@ -1379,32 +1412,32 @@
           <t xml:space="preserve">  支出｜買掛金支払</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="26" t="n"/>
-      <c r="I15" s="26" t="n"/>
-      <c r="J15" s="26" t="n"/>
-      <c r="K15" s="26" t="n"/>
-      <c r="L15" s="26" t="n"/>
-      <c r="M15" s="26" t="n"/>
-      <c r="N15" s="26" t="n"/>
-      <c r="O15" s="26" t="n"/>
-      <c r="P15" s="26" t="n"/>
-      <c r="Q15" s="26" t="n"/>
-      <c r="R15" s="26" t="n"/>
-      <c r="S15" s="26" t="n"/>
-      <c r="T15" s="26" t="n"/>
-      <c r="U15" s="26" t="n"/>
-      <c r="V15" s="26" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="26" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28">
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="28" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n"/>
+      <c r="R15" s="28" t="n"/>
+      <c r="S15" s="28" t="n"/>
+      <c r="T15" s="28" t="n"/>
+      <c r="U15" s="28" t="n"/>
+      <c r="V15" s="28" t="n"/>
+      <c r="W15" s="28" t="n"/>
+      <c r="X15" s="28" t="n"/>
+      <c r="Y15" s="28" t="n"/>
+      <c r="Z15" s="28" t="n"/>
+      <c r="AA15" s="30">
         <f>SUM(B15:Z15)</f>
         <v/>
       </c>
@@ -1415,32 +1448,32 @@
           <t xml:space="preserve">  支出｜支払手形決済</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="26" t="n"/>
-      <c r="M16" s="26" t="n"/>
-      <c r="N16" s="26" t="n"/>
-      <c r="O16" s="26" t="n"/>
-      <c r="P16" s="26" t="n"/>
-      <c r="Q16" s="26" t="n"/>
-      <c r="R16" s="26" t="n"/>
-      <c r="S16" s="26" t="n"/>
-      <c r="T16" s="26" t="n"/>
-      <c r="U16" s="26" t="n"/>
-      <c r="V16" s="26" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="26" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28">
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="28" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n"/>
+      <c r="R16" s="28" t="n"/>
+      <c r="S16" s="28" t="n"/>
+      <c r="T16" s="28" t="n"/>
+      <c r="U16" s="28" t="n"/>
+      <c r="V16" s="28" t="n"/>
+      <c r="W16" s="28" t="n"/>
+      <c r="X16" s="28" t="n"/>
+      <c r="Y16" s="28" t="n"/>
+      <c r="Z16" s="28" t="n"/>
+      <c r="AA16" s="30">
         <f>SUM(B16:Z16)</f>
         <v/>
       </c>
@@ -1451,32 +1484,32 @@
           <t xml:space="preserve">  支出｜未払金支払</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="26" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="26" t="n"/>
-      <c r="I17" s="26" t="n"/>
-      <c r="J17" s="26" t="n"/>
-      <c r="K17" s="26" t="n"/>
-      <c r="L17" s="26" t="n"/>
-      <c r="M17" s="26" t="n"/>
-      <c r="N17" s="26" t="n"/>
-      <c r="O17" s="26" t="n"/>
-      <c r="P17" s="26" t="n"/>
-      <c r="Q17" s="26" t="n"/>
-      <c r="R17" s="26" t="n"/>
-      <c r="S17" s="26" t="n"/>
-      <c r="T17" s="26" t="n"/>
-      <c r="U17" s="26" t="n"/>
-      <c r="V17" s="26" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="26" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28">
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n"/>
+      <c r="R17" s="28" t="n"/>
+      <c r="S17" s="28" t="n"/>
+      <c r="T17" s="28" t="n"/>
+      <c r="U17" s="28" t="n"/>
+      <c r="V17" s="28" t="n"/>
+      <c r="W17" s="28" t="n"/>
+      <c r="X17" s="28" t="n"/>
+      <c r="Y17" s="28" t="n"/>
+      <c r="Z17" s="28" t="n"/>
+      <c r="AA17" s="30">
         <f>SUM(B17:Z17)</f>
         <v/>
       </c>
@@ -1487,82 +1520,82 @@
           <t xml:space="preserve">  支出｜人件費（給与・賞与）</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="28" t="n">
         <v>4800000</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="28" t="n">
         <v>4800000</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="28" t="n">
         <v>4800000</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="28" t="n">
         <v>4800000</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="28" t="n">
         <v>5100000</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="28" t="n">
         <v>5100000</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="28" t="n">
         <v>5100000</v>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="28" t="n">
         <v>5100000</v>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="28" t="n">
         <v>5100000</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="L18" s="26" t="n">
+      <c r="L18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="M18" s="26" t="n">
+      <c r="M18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="N18" s="26" t="n">
+      <c r="N18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="O18" s="26" t="n">
+      <c r="O18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="P18" s="26" t="n">
+      <c r="P18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="Q18" s="26" t="n">
+      <c r="Q18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="R18" s="26" t="n">
+      <c r="R18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="S18" s="26" t="n">
+      <c r="S18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="T18" s="26" t="n">
+      <c r="T18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="U18" s="26" t="n">
+      <c r="U18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="V18" s="26" t="n">
+      <c r="V18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="W18" s="26" t="n">
+      <c r="W18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="X18" s="26" t="n">
+      <c r="X18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="Y18" s="26" t="n">
+      <c r="Y18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="Z18" s="26" t="n">
+      <c r="Z18" s="28" t="n">
         <v>5500000</v>
       </c>
-      <c r="AA18" s="28">
+      <c r="AA18" s="30">
         <f>SUM(B18:Z18)</f>
         <v/>
       </c>
@@ -1573,82 +1606,56 @@
           <t xml:space="preserve">  支出｜法定福利費</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="L19" s="26" t="n">
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="M19" s="26" t="n">
+      <c r="P19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="N19" s="26" t="n">
+      <c r="Q19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="O19" s="26" t="n">
+      <c r="R19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="P19" s="26" t="n">
+      <c r="S19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="Q19" s="26" t="n">
+      <c r="T19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="R19" s="26" t="n">
+      <c r="U19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="S19" s="26" t="n">
+      <c r="V19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="T19" s="26" t="n">
+      <c r="W19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="U19" s="26" t="n">
+      <c r="X19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="V19" s="26" t="n">
+      <c r="Y19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="W19" s="26" t="n">
+      <c r="Z19" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="X19" s="26" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="Y19" s="26" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="Z19" s="26" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="AA19" s="28">
+      <c r="AA19" s="30">
         <f>SUM(B19:Z19)</f>
         <v/>
       </c>
@@ -1659,50 +1666,50 @@
           <t xml:space="preserve">  支出｜住民税その他税</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="D20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="I20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>350000</v>
-      </c>
-      <c r="K20" s="26" t="n"/>
-      <c r="L20" s="26" t="n"/>
-      <c r="M20" s="26" t="n"/>
-      <c r="N20" s="26" t="n"/>
-      <c r="O20" s="26" t="n"/>
-      <c r="P20" s="26" t="n"/>
-      <c r="Q20" s="26" t="n"/>
-      <c r="R20" s="26" t="n"/>
-      <c r="S20" s="26" t="n"/>
-      <c r="T20" s="26" t="n"/>
-      <c r="U20" s="26" t="n"/>
-      <c r="V20" s="26" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
-      <c r="Y20" s="26" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28">
+      <c r="B20" s="28" t="n">
+        <v>335000</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>335000</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>335000</v>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>340000</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>340000</v>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>340000</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>340000</v>
+      </c>
+      <c r="J20" s="28" t="n">
+        <v>340000</v>
+      </c>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="28" t="n"/>
+      <c r="M20" s="28" t="n"/>
+      <c r="N20" s="28" t="n"/>
+      <c r="O20" s="28" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n"/>
+      <c r="R20" s="28" t="n"/>
+      <c r="S20" s="28" t="n"/>
+      <c r="T20" s="28" t="n"/>
+      <c r="U20" s="28" t="n"/>
+      <c r="V20" s="28" t="n"/>
+      <c r="W20" s="28" t="n"/>
+      <c r="X20" s="28" t="n"/>
+      <c r="Y20" s="28" t="n"/>
+      <c r="Z20" s="28" t="n"/>
+      <c r="AA20" s="30">
         <f>SUM(B20:Z20)</f>
         <v/>
       </c>
@@ -1713,50 +1720,50 @@
           <t xml:space="preserve">  支出｜地代家賃</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="H21" s="26" t="n">
+      <c r="H21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="J21" s="26" t="n">
+      <c r="J21" s="28" t="n">
         <v>880000</v>
       </c>
-      <c r="K21" s="26" t="n"/>
-      <c r="L21" s="26" t="n"/>
-      <c r="M21" s="26" t="n"/>
-      <c r="N21" s="26" t="n"/>
-      <c r="O21" s="26" t="n"/>
-      <c r="P21" s="26" t="n"/>
-      <c r="Q21" s="26" t="n"/>
-      <c r="R21" s="26" t="n"/>
-      <c r="S21" s="26" t="n"/>
-      <c r="T21" s="26" t="n"/>
-      <c r="U21" s="26" t="n"/>
-      <c r="V21" s="26" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="26" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28">
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="28" t="n"/>
+      <c r="M21" s="28" t="n"/>
+      <c r="N21" s="28" t="n"/>
+      <c r="O21" s="28" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n"/>
+      <c r="R21" s="28" t="n"/>
+      <c r="S21" s="28" t="n"/>
+      <c r="T21" s="28" t="n"/>
+      <c r="U21" s="28" t="n"/>
+      <c r="V21" s="28" t="n"/>
+      <c r="W21" s="28" t="n"/>
+      <c r="X21" s="28" t="n"/>
+      <c r="Y21" s="28" t="n"/>
+      <c r="Z21" s="28" t="n"/>
+      <c r="AA21" s="30">
         <f>SUM(B21:Z21)</f>
         <v/>
       </c>
@@ -1767,56 +1774,56 @@
           <t xml:space="preserve">  支出｜水道光熱費・通信費</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="H22" s="26" t="n">
+      <c r="H22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="J22" s="26" t="n">
+      <c r="J22" s="28" t="n">
         <v>110000</v>
       </c>
-      <c r="K22" s="26" t="n">
+      <c r="K22" s="28" t="n">
         <v>220000</v>
       </c>
-      <c r="L22" s="26" t="n">
+      <c r="L22" s="28" t="n">
         <v>220000</v>
       </c>
-      <c r="M22" s="26" t="n">
+      <c r="M22" s="28" t="n">
         <v>220000</v>
       </c>
-      <c r="N22" s="26" t="n"/>
-      <c r="O22" s="26" t="n"/>
-      <c r="P22" s="26" t="n"/>
-      <c r="Q22" s="26" t="n"/>
-      <c r="R22" s="26" t="n"/>
-      <c r="S22" s="26" t="n"/>
-      <c r="T22" s="26" t="n"/>
-      <c r="U22" s="26" t="n"/>
-      <c r="V22" s="26" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="26" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28">
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n"/>
+      <c r="R22" s="28" t="n"/>
+      <c r="S22" s="28" t="n"/>
+      <c r="T22" s="28" t="n"/>
+      <c r="U22" s="28" t="n"/>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
+      <c r="X22" s="28" t="n"/>
+      <c r="Y22" s="28" t="n"/>
+      <c r="Z22" s="28" t="n"/>
+      <c r="AA22" s="30">
         <f>SUM(B22:Z22)</f>
         <v/>
       </c>
@@ -1827,56 +1834,56 @@
           <t xml:space="preserve">  支出｜その他販売管理費</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="H23" s="26" t="n">
+      <c r="H23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="J23" s="26" t="n">
+      <c r="J23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="K23" s="26" t="n">
+      <c r="K23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="L23" s="26" t="n">
+      <c r="L23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="M23" s="26" t="n">
+      <c r="M23" s="28" t="n">
         <v>800000</v>
       </c>
-      <c r="N23" s="26" t="n"/>
-      <c r="O23" s="26" t="n"/>
-      <c r="P23" s="26" t="n"/>
-      <c r="Q23" s="26" t="n"/>
-      <c r="R23" s="26" t="n"/>
-      <c r="S23" s="26" t="n"/>
-      <c r="T23" s="26" t="n"/>
-      <c r="U23" s="26" t="n"/>
-      <c r="V23" s="26" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="26" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28">
+      <c r="N23" s="28" t="n"/>
+      <c r="O23" s="28" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n"/>
+      <c r="R23" s="28" t="n"/>
+      <c r="S23" s="28" t="n"/>
+      <c r="T23" s="28" t="n"/>
+      <c r="U23" s="28" t="n"/>
+      <c r="V23" s="28" t="n"/>
+      <c r="W23" s="28" t="n"/>
+      <c r="X23" s="28" t="n"/>
+      <c r="Y23" s="28" t="n"/>
+      <c r="Z23" s="28" t="n"/>
+      <c r="AA23" s="30">
         <f>SUM(B23:Z23)</f>
         <v/>
       </c>
@@ -1887,32 +1894,32 @@
           <t xml:space="preserve">  支出｜支払利息・割引料</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="26" t="n"/>
-      <c r="L24" s="26" t="n"/>
-      <c r="M24" s="26" t="n"/>
-      <c r="N24" s="26" t="n"/>
-      <c r="O24" s="26" t="n"/>
-      <c r="P24" s="26" t="n"/>
-      <c r="Q24" s="26" t="n"/>
-      <c r="R24" s="26" t="n"/>
-      <c r="S24" s="26" t="n"/>
-      <c r="T24" s="26" t="n"/>
-      <c r="U24" s="26" t="n"/>
-      <c r="V24" s="26" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="26" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28">
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="28" t="n"/>
+      <c r="J24" s="28" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="28" t="n"/>
+      <c r="M24" s="28" t="n"/>
+      <c r="N24" s="28" t="n"/>
+      <c r="O24" s="28" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n"/>
+      <c r="R24" s="28" t="n"/>
+      <c r="S24" s="28" t="n"/>
+      <c r="T24" s="28" t="n"/>
+      <c r="U24" s="28" t="n"/>
+      <c r="V24" s="28" t="n"/>
+      <c r="W24" s="28" t="n"/>
+      <c r="X24" s="28" t="n"/>
+      <c r="Y24" s="28" t="n"/>
+      <c r="Z24" s="28" t="n"/>
+      <c r="AA24" s="30">
         <f>SUM(B24:Z24)</f>
         <v/>
       </c>
@@ -1923,107 +1930,107 @@
           <t xml:space="preserve">  支出 計</t>
         </is>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="31">
         <f>SUM(B14:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="31">
         <f>SUM(C14:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="31">
         <f>SUM(D14:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="31">
         <f>SUM(E14:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="31">
         <f>SUM(F14:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="31">
         <f>SUM(G14:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="31">
         <f>SUM(H14:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="31">
         <f>SUM(I14:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="31">
         <f>SUM(J14:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="31">
         <f>SUM(K14:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="31">
         <f>SUM(L14:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="31">
         <f>SUM(M14:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="31">
         <f>SUM(N14:N24)</f>
         <v/>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="31">
         <f>SUM(O14:O24)</f>
         <v/>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="31">
         <f>SUM(P14:P24)</f>
         <v/>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="31">
         <f>SUM(Q14:Q24)</f>
         <v/>
       </c>
-      <c r="R25" s="29">
+      <c r="R25" s="31">
         <f>SUM(R14:R24)</f>
         <v/>
       </c>
-      <c r="S25" s="29">
+      <c r="S25" s="31">
         <f>SUM(S14:S24)</f>
         <v/>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="31">
         <f>SUM(T14:T24)</f>
         <v/>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="31">
         <f>SUM(U14:U24)</f>
         <v/>
       </c>
-      <c r="V25" s="29">
+      <c r="V25" s="31">
         <f>SUM(V14:V24)</f>
         <v/>
       </c>
-      <c r="W25" s="29">
+      <c r="W25" s="31">
         <f>SUM(W14:W24)</f>
         <v/>
       </c>
-      <c r="X25" s="29">
+      <c r="X25" s="31">
         <f>SUM(X14:X24)</f>
         <v/>
       </c>
-      <c r="Y25" s="29">
+      <c r="Y25" s="31">
         <f>SUM(Y14:Y24)</f>
         <v/>
       </c>
-      <c r="Z25" s="29">
+      <c r="Z25" s="31">
         <f>SUM(Z14:Z24)</f>
         <v/>
       </c>
-      <c r="AA25" s="29">
+      <c r="AA25" s="31">
         <f>SUM(AA14:AA24)</f>
         <v/>
       </c>
@@ -2034,107 +2041,107 @@
           <t>経常収支 差額（収入－支出）</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="32">
         <f>B13-B25</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="32">
         <f>C13-C25</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="32">
         <f>D13-D25</f>
         <v/>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="32">
         <f>E13-E25</f>
         <v/>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="32">
         <f>F13-F25</f>
         <v/>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="32">
         <f>G13-G25</f>
         <v/>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="32">
         <f>H13-H25</f>
         <v/>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="32">
         <f>I13-I25</f>
         <v/>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="32">
         <f>J13-J25</f>
         <v/>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="32">
         <f>K13-K25</f>
         <v/>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="32">
         <f>L13-L25</f>
         <v/>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="32">
         <f>M13-M25</f>
         <v/>
       </c>
-      <c r="N26" s="30">
+      <c r="N26" s="32">
         <f>N13-N25</f>
         <v/>
       </c>
-      <c r="O26" s="30">
+      <c r="O26" s="32">
         <f>O13-O25</f>
         <v/>
       </c>
-      <c r="P26" s="30">
+      <c r="P26" s="32">
         <f>P13-P25</f>
         <v/>
       </c>
-      <c r="Q26" s="30">
+      <c r="Q26" s="32">
         <f>Q13-Q25</f>
         <v/>
       </c>
-      <c r="R26" s="30">
+      <c r="R26" s="32">
         <f>R13-R25</f>
         <v/>
       </c>
-      <c r="S26" s="30">
+      <c r="S26" s="32">
         <f>S13-S25</f>
         <v/>
       </c>
-      <c r="T26" s="30">
+      <c r="T26" s="32">
         <f>T13-T25</f>
         <v/>
       </c>
-      <c r="U26" s="30">
+      <c r="U26" s="32">
         <f>U13-U25</f>
         <v/>
       </c>
-      <c r="V26" s="30">
+      <c r="V26" s="32">
         <f>V13-V25</f>
         <v/>
       </c>
-      <c r="W26" s="30">
+      <c r="W26" s="32">
         <f>W13-W25</f>
         <v/>
       </c>
-      <c r="X26" s="30">
+      <c r="X26" s="32">
         <f>X13-X25</f>
         <v/>
       </c>
-      <c r="Y26" s="30">
+      <c r="Y26" s="32">
         <f>Y13-Y25</f>
         <v/>
       </c>
-      <c r="Z26" s="30">
+      <c r="Z26" s="32">
         <f>Z13-Z25</f>
         <v/>
       </c>
-      <c r="AA26" s="30">
+      <c r="AA26" s="32">
         <f>AA13-AA25</f>
         <v/>
       </c>
@@ -2145,32 +2152,32 @@
           <t>経常外収支</t>
         </is>
       </c>
-      <c r="B27" s="27" t="n"/>
-      <c r="C27" s="27" t="n"/>
-      <c r="D27" s="27" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
-      <c r="H27" s="27" t="n"/>
-      <c r="I27" s="27" t="n"/>
-      <c r="J27" s="27" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="27" t="n"/>
-      <c r="O27" s="27" t="n"/>
-      <c r="P27" s="27" t="n"/>
-      <c r="Q27" s="27" t="n"/>
-      <c r="R27" s="27" t="n"/>
-      <c r="S27" s="27" t="n"/>
-      <c r="T27" s="27" t="n"/>
-      <c r="U27" s="27" t="n"/>
-      <c r="V27" s="27" t="n"/>
-      <c r="W27" s="27" t="n"/>
-      <c r="X27" s="27" t="n"/>
-      <c r="Y27" s="27" t="n"/>
-      <c r="Z27" s="27" t="n"/>
-      <c r="AA27" s="27" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="29" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="29" t="n"/>
+      <c r="K27" s="29" t="n"/>
+      <c r="L27" s="29" t="n"/>
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="29" t="n"/>
+      <c r="O27" s="29" t="n"/>
+      <c r="P27" s="29" t="n"/>
+      <c r="Q27" s="29" t="n"/>
+      <c r="R27" s="29" t="n"/>
+      <c r="S27" s="29" t="n"/>
+      <c r="T27" s="29" t="n"/>
+      <c r="U27" s="29" t="n"/>
+      <c r="V27" s="29" t="n"/>
+      <c r="W27" s="29" t="n"/>
+      <c r="X27" s="29" t="n"/>
+      <c r="Y27" s="29" t="n"/>
+      <c r="Z27" s="29" t="n"/>
+      <c r="AA27" s="29" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2178,32 +2185,32 @@
           <t xml:space="preserve">  収入｜固定資産売却収入</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
-      <c r="H28" s="26" t="n"/>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="26" t="n"/>
-      <c r="K28" s="26" t="n"/>
-      <c r="L28" s="26" t="n"/>
-      <c r="M28" s="26" t="n"/>
-      <c r="N28" s="26" t="n"/>
-      <c r="O28" s="26" t="n"/>
-      <c r="P28" s="26" t="n"/>
-      <c r="Q28" s="26" t="n"/>
-      <c r="R28" s="26" t="n"/>
-      <c r="S28" s="26" t="n"/>
-      <c r="T28" s="26" t="n"/>
-      <c r="U28" s="26" t="n"/>
-      <c r="V28" s="26" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
-      <c r="Y28" s="26" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28">
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="28" t="n"/>
+      <c r="J28" s="28" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="28" t="n"/>
+      <c r="M28" s="28" t="n"/>
+      <c r="N28" s="28" t="n"/>
+      <c r="O28" s="28" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n"/>
+      <c r="R28" s="28" t="n"/>
+      <c r="S28" s="28" t="n"/>
+      <c r="T28" s="28" t="n"/>
+      <c r="U28" s="28" t="n"/>
+      <c r="V28" s="28" t="n"/>
+      <c r="W28" s="28" t="n"/>
+      <c r="X28" s="28" t="n"/>
+      <c r="Y28" s="28" t="n"/>
+      <c r="Z28" s="28" t="n"/>
+      <c r="AA28" s="30">
         <f>SUM(B28:Z28)</f>
         <v/>
       </c>
@@ -2214,32 +2221,32 @@
           <t xml:space="preserve">  収入｜保険金・補助金等</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-      <c r="G29" s="26" t="n"/>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="26" t="n"/>
-      <c r="J29" s="26" t="n"/>
-      <c r="K29" s="26" t="n"/>
-      <c r="L29" s="26" t="n"/>
-      <c r="M29" s="26" t="n"/>
-      <c r="N29" s="26" t="n"/>
-      <c r="O29" s="26" t="n"/>
-      <c r="P29" s="26" t="n"/>
-      <c r="Q29" s="26" t="n"/>
-      <c r="R29" s="26" t="n"/>
-      <c r="S29" s="26" t="n"/>
-      <c r="T29" s="26" t="n"/>
-      <c r="U29" s="26" t="n"/>
-      <c r="V29" s="26" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
-      <c r="Y29" s="26" t="n"/>
-      <c r="Z29" s="26" t="n"/>
-      <c r="AA29" s="28">
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="28" t="n"/>
+      <c r="J29" s="28" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="28" t="n"/>
+      <c r="M29" s="28" t="n"/>
+      <c r="N29" s="28" t="n"/>
+      <c r="O29" s="28" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n"/>
+      <c r="R29" s="28" t="n"/>
+      <c r="S29" s="28" t="n"/>
+      <c r="T29" s="28" t="n"/>
+      <c r="U29" s="28" t="n"/>
+      <c r="V29" s="28" t="n"/>
+      <c r="W29" s="28" t="n"/>
+      <c r="X29" s="28" t="n"/>
+      <c r="Y29" s="28" t="n"/>
+      <c r="Z29" s="28" t="n"/>
+      <c r="AA29" s="30">
         <f>SUM(B29:Z29)</f>
         <v/>
       </c>
@@ -2250,32 +2257,32 @@
           <t xml:space="preserve">  収入｜その他</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
-      <c r="H30" s="26" t="n"/>
-      <c r="I30" s="26" t="n"/>
-      <c r="J30" s="26" t="n"/>
-      <c r="K30" s="26" t="n"/>
-      <c r="L30" s="26" t="n"/>
-      <c r="M30" s="26" t="n"/>
-      <c r="N30" s="26" t="n"/>
-      <c r="O30" s="26" t="n"/>
-      <c r="P30" s="26" t="n"/>
-      <c r="Q30" s="26" t="n"/>
-      <c r="R30" s="26" t="n"/>
-      <c r="S30" s="26" t="n"/>
-      <c r="T30" s="26" t="n"/>
-      <c r="U30" s="26" t="n"/>
-      <c r="V30" s="26" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
-      <c r="Y30" s="26" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28">
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="28" t="n"/>
+      <c r="J30" s="28" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="28" t="n"/>
+      <c r="M30" s="28" t="n"/>
+      <c r="N30" s="28" t="n"/>
+      <c r="O30" s="28" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n"/>
+      <c r="R30" s="28" t="n"/>
+      <c r="S30" s="28" t="n"/>
+      <c r="T30" s="28" t="n"/>
+      <c r="U30" s="28" t="n"/>
+      <c r="V30" s="28" t="n"/>
+      <c r="W30" s="28" t="n"/>
+      <c r="X30" s="28" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="30">
         <f>SUM(B30:Z30)</f>
         <v/>
       </c>
@@ -2286,107 +2293,107 @@
           <t xml:space="preserve">  収入 計</t>
         </is>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="31">
         <f>SUM(B28:B30)</f>
         <v/>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="31">
         <f>SUM(C28:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="31">
         <f>SUM(D28:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="31">
         <f>SUM(E28:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="31">
         <f>SUM(F28:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="31">
         <f>SUM(G28:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="31">
         <f>SUM(H28:H30)</f>
         <v/>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="31">
         <f>SUM(I28:I30)</f>
         <v/>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="31">
         <f>SUM(J28:J30)</f>
         <v/>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="31">
         <f>SUM(K28:K30)</f>
         <v/>
       </c>
-      <c r="L31" s="29">
+      <c r="L31" s="31">
         <f>SUM(L28:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="29">
+      <c r="M31" s="31">
         <f>SUM(M28:M30)</f>
         <v/>
       </c>
-      <c r="N31" s="29">
+      <c r="N31" s="31">
         <f>SUM(N28:N30)</f>
         <v/>
       </c>
-      <c r="O31" s="29">
+      <c r="O31" s="31">
         <f>SUM(O28:O30)</f>
         <v/>
       </c>
-      <c r="P31" s="29">
+      <c r="P31" s="31">
         <f>SUM(P28:P30)</f>
         <v/>
       </c>
-      <c r="Q31" s="29">
+      <c r="Q31" s="31">
         <f>SUM(Q28:Q30)</f>
         <v/>
       </c>
-      <c r="R31" s="29">
+      <c r="R31" s="31">
         <f>SUM(R28:R30)</f>
         <v/>
       </c>
-      <c r="S31" s="29">
+      <c r="S31" s="31">
         <f>SUM(S28:S30)</f>
         <v/>
       </c>
-      <c r="T31" s="29">
+      <c r="T31" s="31">
         <f>SUM(T28:T30)</f>
         <v/>
       </c>
-      <c r="U31" s="29">
+      <c r="U31" s="31">
         <f>SUM(U28:U30)</f>
         <v/>
       </c>
-      <c r="V31" s="29">
+      <c r="V31" s="31">
         <f>SUM(V28:V30)</f>
         <v/>
       </c>
-      <c r="W31" s="29">
+      <c r="W31" s="31">
         <f>SUM(W28:W30)</f>
         <v/>
       </c>
-      <c r="X31" s="29">
+      <c r="X31" s="31">
         <f>SUM(X28:X30)</f>
         <v/>
       </c>
-      <c r="Y31" s="29">
+      <c r="Y31" s="31">
         <f>SUM(Y28:Y30)</f>
         <v/>
       </c>
-      <c r="Z31" s="29">
+      <c r="Z31" s="31">
         <f>SUM(Z28:Z30)</f>
         <v/>
       </c>
-      <c r="AA31" s="29">
+      <c r="AA31" s="31">
         <f>SUM(AA28:AA30)</f>
         <v/>
       </c>
@@ -2397,32 +2404,32 @@
           <t xml:space="preserve">  支出｜設備投資（固定資産購入）</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="26" t="n"/>
-      <c r="M32" s="26" t="n"/>
-      <c r="N32" s="26" t="n"/>
-      <c r="O32" s="26" t="n"/>
-      <c r="P32" s="26" t="n"/>
-      <c r="Q32" s="26" t="n"/>
-      <c r="R32" s="26" t="n"/>
-      <c r="S32" s="26" t="n"/>
-      <c r="T32" s="26" t="n"/>
-      <c r="U32" s="26" t="n"/>
-      <c r="V32" s="26" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="26" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="28">
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="28" t="n"/>
+      <c r="J32" s="28" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="28" t="n"/>
+      <c r="M32" s="28" t="n"/>
+      <c r="N32" s="28" t="n"/>
+      <c r="O32" s="28" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n"/>
+      <c r="R32" s="28" t="n"/>
+      <c r="S32" s="28" t="n"/>
+      <c r="T32" s="28" t="n"/>
+      <c r="U32" s="28" t="n"/>
+      <c r="V32" s="28" t="n"/>
+      <c r="W32" s="28" t="n"/>
+      <c r="X32" s="28" t="n"/>
+      <c r="Y32" s="28" t="n"/>
+      <c r="Z32" s="28" t="n"/>
+      <c r="AA32" s="30">
         <f>SUM(B32:Z32)</f>
         <v/>
       </c>
@@ -2433,32 +2440,32 @@
           <t xml:space="preserve">  支出｜法人税・消費税等納付</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="26" t="n"/>
-      <c r="G33" s="26" t="n"/>
-      <c r="H33" s="26" t="n"/>
-      <c r="I33" s="26" t="n"/>
-      <c r="J33" s="26" t="n"/>
-      <c r="K33" s="26" t="n"/>
-      <c r="L33" s="26" t="n"/>
-      <c r="M33" s="26" t="n"/>
-      <c r="N33" s="26" t="n"/>
-      <c r="O33" s="26" t="n"/>
-      <c r="P33" s="26" t="n"/>
-      <c r="Q33" s="26" t="n"/>
-      <c r="R33" s="26" t="n"/>
-      <c r="S33" s="26" t="n"/>
-      <c r="T33" s="26" t="n"/>
-      <c r="U33" s="26" t="n"/>
-      <c r="V33" s="26" t="n"/>
-      <c r="W33" s="26" t="n"/>
-      <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="26" t="n"/>
-      <c r="Z33" s="26" t="n"/>
-      <c r="AA33" s="28">
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="n"/>
+      <c r="O33" s="28" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n"/>
+      <c r="R33" s="28" t="n"/>
+      <c r="S33" s="28" t="n"/>
+      <c r="T33" s="28" t="n"/>
+      <c r="U33" s="28" t="n"/>
+      <c r="V33" s="28" t="n"/>
+      <c r="W33" s="28" t="n"/>
+      <c r="X33" s="28" t="n"/>
+      <c r="Y33" s="28" t="n"/>
+      <c r="Z33" s="28" t="n"/>
+      <c r="AA33" s="30">
         <f>SUM(B33:Z33)</f>
         <v/>
       </c>
@@ -2469,32 +2476,32 @@
           <t xml:space="preserve">  支出｜その他</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="26" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="26" t="n"/>
-      <c r="M34" s="26" t="n"/>
-      <c r="N34" s="26" t="n"/>
-      <c r="O34" s="26" t="n"/>
-      <c r="P34" s="26" t="n"/>
-      <c r="Q34" s="26" t="n"/>
-      <c r="R34" s="26" t="n"/>
-      <c r="S34" s="26" t="n"/>
-      <c r="T34" s="26" t="n"/>
-      <c r="U34" s="26" t="n"/>
-      <c r="V34" s="26" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="26" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="28">
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="28" t="n"/>
+      <c r="J34" s="28" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="28" t="n"/>
+      <c r="M34" s="28" t="n"/>
+      <c r="N34" s="28" t="n"/>
+      <c r="O34" s="28" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n"/>
+      <c r="R34" s="28" t="n"/>
+      <c r="S34" s="28" t="n"/>
+      <c r="T34" s="28" t="n"/>
+      <c r="U34" s="28" t="n"/>
+      <c r="V34" s="28" t="n"/>
+      <c r="W34" s="28" t="n"/>
+      <c r="X34" s="28" t="n"/>
+      <c r="Y34" s="28" t="n"/>
+      <c r="Z34" s="28" t="n"/>
+      <c r="AA34" s="30">
         <f>SUM(B34:Z34)</f>
         <v/>
       </c>
@@ -2505,107 +2512,107 @@
           <t xml:space="preserve">  支出 計</t>
         </is>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="31">
         <f>SUM(B32:B34)</f>
         <v/>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="31">
         <f>SUM(C32:C34)</f>
         <v/>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="31">
         <f>SUM(D32:D34)</f>
         <v/>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="31">
         <f>SUM(E32:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="31">
         <f>SUM(F32:F34)</f>
         <v/>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="31">
         <f>SUM(G32:G34)</f>
         <v/>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="31">
         <f>SUM(H32:H34)</f>
         <v/>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="31">
         <f>SUM(I32:I34)</f>
         <v/>
       </c>
-      <c r="J35" s="29">
+      <c r="J35" s="31">
         <f>SUM(J32:J34)</f>
         <v/>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="31">
         <f>SUM(K32:K34)</f>
         <v/>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="31">
         <f>SUM(L32:L34)</f>
         <v/>
       </c>
-      <c r="M35" s="29">
+      <c r="M35" s="31">
         <f>SUM(M32:M34)</f>
         <v/>
       </c>
-      <c r="N35" s="29">
+      <c r="N35" s="31">
         <f>SUM(N32:N34)</f>
         <v/>
       </c>
-      <c r="O35" s="29">
+      <c r="O35" s="31">
         <f>SUM(O32:O34)</f>
         <v/>
       </c>
-      <c r="P35" s="29">
+      <c r="P35" s="31">
         <f>SUM(P32:P34)</f>
         <v/>
       </c>
-      <c r="Q35" s="29">
+      <c r="Q35" s="31">
         <f>SUM(Q32:Q34)</f>
         <v/>
       </c>
-      <c r="R35" s="29">
+      <c r="R35" s="31">
         <f>SUM(R32:R34)</f>
         <v/>
       </c>
-      <c r="S35" s="29">
+      <c r="S35" s="31">
         <f>SUM(S32:S34)</f>
         <v/>
       </c>
-      <c r="T35" s="29">
+      <c r="T35" s="31">
         <f>SUM(T32:T34)</f>
         <v/>
       </c>
-      <c r="U35" s="29">
+      <c r="U35" s="31">
         <f>SUM(U32:U34)</f>
         <v/>
       </c>
-      <c r="V35" s="29">
+      <c r="V35" s="31">
         <f>SUM(V32:V34)</f>
         <v/>
       </c>
-      <c r="W35" s="29">
+      <c r="W35" s="31">
         <f>SUM(W32:W34)</f>
         <v/>
       </c>
-      <c r="X35" s="29">
+      <c r="X35" s="31">
         <f>SUM(X32:X34)</f>
         <v/>
       </c>
-      <c r="Y35" s="29">
+      <c r="Y35" s="31">
         <f>SUM(Y32:Y34)</f>
         <v/>
       </c>
-      <c r="Z35" s="29">
+      <c r="Z35" s="31">
         <f>SUM(Z32:Z34)</f>
         <v/>
       </c>
-      <c r="AA35" s="29">
+      <c r="AA35" s="31">
         <f>SUM(AA32:AA34)</f>
         <v/>
       </c>
@@ -2616,107 +2623,107 @@
           <t>経常外収支 差額（収入－支出）</t>
         </is>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="32">
         <f>B31-B35</f>
         <v/>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="32">
         <f>C31-C35</f>
         <v/>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="32">
         <f>D31-D35</f>
         <v/>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="32">
         <f>E31-E35</f>
         <v/>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="32">
         <f>F31-F35</f>
         <v/>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="32">
         <f>G31-G35</f>
         <v/>
       </c>
-      <c r="H36" s="30">
+      <c r="H36" s="32">
         <f>H31-H35</f>
         <v/>
       </c>
-      <c r="I36" s="30">
+      <c r="I36" s="32">
         <f>I31-I35</f>
         <v/>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="32">
         <f>J31-J35</f>
         <v/>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="32">
         <f>K31-K35</f>
         <v/>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="32">
         <f>L31-L35</f>
         <v/>
       </c>
-      <c r="M36" s="30">
+      <c r="M36" s="32">
         <f>M31-M35</f>
         <v/>
       </c>
-      <c r="N36" s="30">
+      <c r="N36" s="32">
         <f>N31-N35</f>
         <v/>
       </c>
-      <c r="O36" s="30">
+      <c r="O36" s="32">
         <f>O31-O35</f>
         <v/>
       </c>
-      <c r="P36" s="30">
+      <c r="P36" s="32">
         <f>P31-P35</f>
         <v/>
       </c>
-      <c r="Q36" s="30">
+      <c r="Q36" s="32">
         <f>Q31-Q35</f>
         <v/>
       </c>
-      <c r="R36" s="30">
+      <c r="R36" s="32">
         <f>R31-R35</f>
         <v/>
       </c>
-      <c r="S36" s="30">
+      <c r="S36" s="32">
         <f>S31-S35</f>
         <v/>
       </c>
-      <c r="T36" s="30">
+      <c r="T36" s="32">
         <f>T31-T35</f>
         <v/>
       </c>
-      <c r="U36" s="30">
+      <c r="U36" s="32">
         <f>U31-U35</f>
         <v/>
       </c>
-      <c r="V36" s="30">
+      <c r="V36" s="32">
         <f>V31-V35</f>
         <v/>
       </c>
-      <c r="W36" s="30">
+      <c r="W36" s="32">
         <f>W31-W35</f>
         <v/>
       </c>
-      <c r="X36" s="30">
+      <c r="X36" s="32">
         <f>X31-X35</f>
         <v/>
       </c>
-      <c r="Y36" s="30">
+      <c r="Y36" s="32">
         <f>Y31-Y35</f>
         <v/>
       </c>
-      <c r="Z36" s="30">
+      <c r="Z36" s="32">
         <f>Z31-Z35</f>
         <v/>
       </c>
-      <c r="AA36" s="30">
+      <c r="AA36" s="32">
         <f>AA31-AA35</f>
         <v/>
       </c>
@@ -2727,32 +2734,32 @@
           <t>財務収支</t>
         </is>
       </c>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="27" t="n"/>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-      <c r="P37" s="27" t="n"/>
-      <c r="Q37" s="27" t="n"/>
-      <c r="R37" s="27" t="n"/>
-      <c r="S37" s="27" t="n"/>
-      <c r="T37" s="27" t="n"/>
-      <c r="U37" s="27" t="n"/>
-      <c r="V37" s="27" t="n"/>
-      <c r="W37" s="27" t="n"/>
-      <c r="X37" s="27" t="n"/>
-      <c r="Y37" s="27" t="n"/>
-      <c r="Z37" s="27" t="n"/>
-      <c r="AA37" s="27" t="n"/>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="29" t="n"/>
+      <c r="H37" s="29" t="n"/>
+      <c r="I37" s="29" t="n"/>
+      <c r="J37" s="29" t="n"/>
+      <c r="K37" s="29" t="n"/>
+      <c r="L37" s="29" t="n"/>
+      <c r="M37" s="29" t="n"/>
+      <c r="N37" s="29" t="n"/>
+      <c r="O37" s="29" t="n"/>
+      <c r="P37" s="29" t="n"/>
+      <c r="Q37" s="29" t="n"/>
+      <c r="R37" s="29" t="n"/>
+      <c r="S37" s="29" t="n"/>
+      <c r="T37" s="29" t="n"/>
+      <c r="U37" s="29" t="n"/>
+      <c r="V37" s="29" t="n"/>
+      <c r="W37" s="29" t="n"/>
+      <c r="X37" s="29" t="n"/>
+      <c r="Y37" s="29" t="n"/>
+      <c r="Z37" s="29" t="n"/>
+      <c r="AA37" s="29" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2760,32 +2767,32 @@
           <t xml:space="preserve">  収入｜借入金</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
-      <c r="H38" s="26" t="n"/>
-      <c r="I38" s="26" t="n"/>
-      <c r="J38" s="26" t="n"/>
-      <c r="K38" s="26" t="n"/>
-      <c r="L38" s="26" t="n"/>
-      <c r="M38" s="26" t="n"/>
-      <c r="N38" s="26" t="n"/>
-      <c r="O38" s="26" t="n"/>
-      <c r="P38" s="26" t="n"/>
-      <c r="Q38" s="26" t="n"/>
-      <c r="R38" s="26" t="n"/>
-      <c r="S38" s="26" t="n"/>
-      <c r="T38" s="26" t="n"/>
-      <c r="U38" s="26" t="n"/>
-      <c r="V38" s="26" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="26" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28">
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="28" t="n"/>
+      <c r="J38" s="28" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="28" t="n"/>
+      <c r="M38" s="28" t="n"/>
+      <c r="N38" s="28" t="n"/>
+      <c r="O38" s="28" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n"/>
+      <c r="R38" s="28" t="n"/>
+      <c r="S38" s="28" t="n"/>
+      <c r="T38" s="28" t="n"/>
+      <c r="U38" s="28" t="n"/>
+      <c r="V38" s="28" t="n"/>
+      <c r="W38" s="28" t="n"/>
+      <c r="X38" s="28" t="n"/>
+      <c r="Y38" s="28" t="n"/>
+      <c r="Z38" s="28" t="n"/>
+      <c r="AA38" s="30">
         <f>SUM(B38:Z38)</f>
         <v/>
       </c>
@@ -2796,32 +2803,32 @@
           <t xml:space="preserve">  収入｜増資・出資</t>
         </is>
       </c>
-      <c r="B39" s="26" t="n"/>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="26" t="n"/>
-      <c r="G39" s="26" t="n"/>
-      <c r="H39" s="26" t="n"/>
-      <c r="I39" s="26" t="n"/>
-      <c r="J39" s="26" t="n"/>
-      <c r="K39" s="26" t="n"/>
-      <c r="L39" s="26" t="n"/>
-      <c r="M39" s="26" t="n"/>
-      <c r="N39" s="26" t="n"/>
-      <c r="O39" s="26" t="n"/>
-      <c r="P39" s="26" t="n"/>
-      <c r="Q39" s="26" t="n"/>
-      <c r="R39" s="26" t="n"/>
-      <c r="S39" s="26" t="n"/>
-      <c r="T39" s="26" t="n"/>
-      <c r="U39" s="26" t="n"/>
-      <c r="V39" s="26" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="26" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="28">
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="28" t="n"/>
+      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="28" t="n"/>
+      <c r="M39" s="28" t="n"/>
+      <c r="N39" s="28" t="n"/>
+      <c r="O39" s="28" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n"/>
+      <c r="R39" s="28" t="n"/>
+      <c r="S39" s="28" t="n"/>
+      <c r="T39" s="28" t="n"/>
+      <c r="U39" s="28" t="n"/>
+      <c r="V39" s="28" t="n"/>
+      <c r="W39" s="28" t="n"/>
+      <c r="X39" s="28" t="n"/>
+      <c r="Y39" s="28" t="n"/>
+      <c r="Z39" s="28" t="n"/>
+      <c r="AA39" s="30">
         <f>SUM(B39:Z39)</f>
         <v/>
       </c>
@@ -2832,32 +2839,32 @@
           <t xml:space="preserve">  収入｜その他</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n"/>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="26" t="n"/>
-      <c r="K40" s="26" t="n"/>
-      <c r="L40" s="26" t="n"/>
-      <c r="M40" s="26" t="n"/>
-      <c r="N40" s="26" t="n"/>
-      <c r="O40" s="26" t="n"/>
-      <c r="P40" s="26" t="n"/>
-      <c r="Q40" s="26" t="n"/>
-      <c r="R40" s="26" t="n"/>
-      <c r="S40" s="26" t="n"/>
-      <c r="T40" s="26" t="n"/>
-      <c r="U40" s="26" t="n"/>
-      <c r="V40" s="26" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="26" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="28">
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="28" t="n"/>
+      <c r="J40" s="28" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="28" t="n"/>
+      <c r="M40" s="28" t="n"/>
+      <c r="N40" s="28" t="n"/>
+      <c r="O40" s="28" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n"/>
+      <c r="R40" s="28" t="n"/>
+      <c r="S40" s="28" t="n"/>
+      <c r="T40" s="28" t="n"/>
+      <c r="U40" s="28" t="n"/>
+      <c r="V40" s="28" t="n"/>
+      <c r="W40" s="28" t="n"/>
+      <c r="X40" s="28" t="n"/>
+      <c r="Y40" s="28" t="n"/>
+      <c r="Z40" s="28" t="n"/>
+      <c r="AA40" s="30">
         <f>SUM(B40:Z40)</f>
         <v/>
       </c>
@@ -2868,107 +2875,107 @@
           <t xml:space="preserve">  収入 計</t>
         </is>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="31">
         <f>SUM(B38:B40)</f>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="31">
         <f>SUM(C38:C40)</f>
         <v/>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="31">
         <f>SUM(D38:D40)</f>
         <v/>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="31">
         <f>SUM(E38:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="31">
         <f>SUM(F38:F40)</f>
         <v/>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="31">
         <f>SUM(G38:G40)</f>
         <v/>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="31">
         <f>SUM(H38:H40)</f>
         <v/>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="31">
         <f>SUM(I38:I40)</f>
         <v/>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="31">
         <f>SUM(J38:J40)</f>
         <v/>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="31">
         <f>SUM(K38:K40)</f>
         <v/>
       </c>
-      <c r="L41" s="29">
+      <c r="L41" s="31">
         <f>SUM(L38:L40)</f>
         <v/>
       </c>
-      <c r="M41" s="29">
+      <c r="M41" s="31">
         <f>SUM(M38:M40)</f>
         <v/>
       </c>
-      <c r="N41" s="29">
+      <c r="N41" s="31">
         <f>SUM(N38:N40)</f>
         <v/>
       </c>
-      <c r="O41" s="29">
+      <c r="O41" s="31">
         <f>SUM(O38:O40)</f>
         <v/>
       </c>
-      <c r="P41" s="29">
+      <c r="P41" s="31">
         <f>SUM(P38:P40)</f>
         <v/>
       </c>
-      <c r="Q41" s="29">
+      <c r="Q41" s="31">
         <f>SUM(Q38:Q40)</f>
         <v/>
       </c>
-      <c r="R41" s="29">
+      <c r="R41" s="31">
         <f>SUM(R38:R40)</f>
         <v/>
       </c>
-      <c r="S41" s="29">
+      <c r="S41" s="31">
         <f>SUM(S38:S40)</f>
         <v/>
       </c>
-      <c r="T41" s="29">
+      <c r="T41" s="31">
         <f>SUM(T38:T40)</f>
         <v/>
       </c>
-      <c r="U41" s="29">
+      <c r="U41" s="31">
         <f>SUM(U38:U40)</f>
         <v/>
       </c>
-      <c r="V41" s="29">
+      <c r="V41" s="31">
         <f>SUM(V38:V40)</f>
         <v/>
       </c>
-      <c r="W41" s="29">
+      <c r="W41" s="31">
         <f>SUM(W38:W40)</f>
         <v/>
       </c>
-      <c r="X41" s="29">
+      <c r="X41" s="31">
         <f>SUM(X38:X40)</f>
         <v/>
       </c>
-      <c r="Y41" s="29">
+      <c r="Y41" s="31">
         <f>SUM(Y38:Y40)</f>
         <v/>
       </c>
-      <c r="Z41" s="29">
+      <c r="Z41" s="31">
         <f>SUM(Z38:Z40)</f>
         <v/>
       </c>
-      <c r="AA41" s="29">
+      <c r="AA41" s="31">
         <f>SUM(AA38:AA40)</f>
         <v/>
       </c>
@@ -2979,32 +2986,32 @@
           <t xml:space="preserve">  支出｜借入金返済</t>
         </is>
       </c>
-      <c r="B42" s="26" t="n"/>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
-      <c r="H42" s="26" t="n"/>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="26" t="n"/>
-      <c r="K42" s="26" t="n"/>
-      <c r="L42" s="26" t="n"/>
-      <c r="M42" s="26" t="n"/>
-      <c r="N42" s="26" t="n"/>
-      <c r="O42" s="26" t="n"/>
-      <c r="P42" s="26" t="n"/>
-      <c r="Q42" s="26" t="n"/>
-      <c r="R42" s="26" t="n"/>
-      <c r="S42" s="26" t="n"/>
-      <c r="T42" s="26" t="n"/>
-      <c r="U42" s="26" t="n"/>
-      <c r="V42" s="26" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="26" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28">
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="28" t="n"/>
+      <c r="J42" s="28" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="28" t="n"/>
+      <c r="M42" s="28" t="n"/>
+      <c r="N42" s="28" t="n"/>
+      <c r="O42" s="28" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n"/>
+      <c r="R42" s="28" t="n"/>
+      <c r="S42" s="28" t="n"/>
+      <c r="T42" s="28" t="n"/>
+      <c r="U42" s="28" t="n"/>
+      <c r="V42" s="28" t="n"/>
+      <c r="W42" s="28" t="n"/>
+      <c r="X42" s="28" t="n"/>
+      <c r="Y42" s="28" t="n"/>
+      <c r="Z42" s="28" t="n"/>
+      <c r="AA42" s="30">
         <f>SUM(B42:Z42)</f>
         <v/>
       </c>
@@ -3015,32 +3022,32 @@
           <t xml:space="preserve">  支出｜配当金・役員借入返済</t>
         </is>
       </c>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="26" t="n"/>
-      <c r="G43" s="26" t="n"/>
-      <c r="H43" s="26" t="n"/>
-      <c r="I43" s="26" t="n"/>
-      <c r="J43" s="26" t="n"/>
-      <c r="K43" s="26" t="n"/>
-      <c r="L43" s="26" t="n"/>
-      <c r="M43" s="26" t="n"/>
-      <c r="N43" s="26" t="n"/>
-      <c r="O43" s="26" t="n"/>
-      <c r="P43" s="26" t="n"/>
-      <c r="Q43" s="26" t="n"/>
-      <c r="R43" s="26" t="n"/>
-      <c r="S43" s="26" t="n"/>
-      <c r="T43" s="26" t="n"/>
-      <c r="U43" s="26" t="n"/>
-      <c r="V43" s="26" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="26" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28">
+      <c r="B43" s="28" t="n"/>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="28" t="n"/>
+      <c r="J43" s="28" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="28" t="n"/>
+      <c r="M43" s="28" t="n"/>
+      <c r="N43" s="28" t="n"/>
+      <c r="O43" s="28" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n"/>
+      <c r="R43" s="28" t="n"/>
+      <c r="S43" s="28" t="n"/>
+      <c r="T43" s="28" t="n"/>
+      <c r="U43" s="28" t="n"/>
+      <c r="V43" s="28" t="n"/>
+      <c r="W43" s="28" t="n"/>
+      <c r="X43" s="28" t="n"/>
+      <c r="Y43" s="28" t="n"/>
+      <c r="Z43" s="28" t="n"/>
+      <c r="AA43" s="30">
         <f>SUM(B43:Z43)</f>
         <v/>
       </c>
@@ -3051,32 +3058,32 @@
           <t xml:space="preserve">  支出｜その他</t>
         </is>
       </c>
-      <c r="B44" s="26" t="n"/>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="26" t="n"/>
-      <c r="H44" s="26" t="n"/>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="26" t="n"/>
-      <c r="K44" s="26" t="n"/>
-      <c r="L44" s="26" t="n"/>
-      <c r="M44" s="26" t="n"/>
-      <c r="N44" s="26" t="n"/>
-      <c r="O44" s="26" t="n"/>
-      <c r="P44" s="26" t="n"/>
-      <c r="Q44" s="26" t="n"/>
-      <c r="R44" s="26" t="n"/>
-      <c r="S44" s="26" t="n"/>
-      <c r="T44" s="26" t="n"/>
-      <c r="U44" s="26" t="n"/>
-      <c r="V44" s="26" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="26" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28">
+      <c r="B44" s="28" t="n"/>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="28" t="n"/>
+      <c r="J44" s="28" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="28" t="n"/>
+      <c r="M44" s="28" t="n"/>
+      <c r="N44" s="28" t="n"/>
+      <c r="O44" s="28" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n"/>
+      <c r="R44" s="28" t="n"/>
+      <c r="S44" s="28" t="n"/>
+      <c r="T44" s="28" t="n"/>
+      <c r="U44" s="28" t="n"/>
+      <c r="V44" s="28" t="n"/>
+      <c r="W44" s="28" t="n"/>
+      <c r="X44" s="28" t="n"/>
+      <c r="Y44" s="28" t="n"/>
+      <c r="Z44" s="28" t="n"/>
+      <c r="AA44" s="30">
         <f>SUM(B44:Z44)</f>
         <v/>
       </c>
@@ -3087,107 +3094,107 @@
           <t xml:space="preserve">  支出 計</t>
         </is>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="31">
         <f>SUM(B42:B44)</f>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="31">
         <f>SUM(C42:C44)</f>
         <v/>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="31">
         <f>SUM(D42:D44)</f>
         <v/>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="31">
         <f>SUM(E42:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="31">
         <f>SUM(F42:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="31">
         <f>SUM(G42:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="29">
+      <c r="H45" s="31">
         <f>SUM(H42:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="31">
         <f>SUM(I42:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="29">
+      <c r="J45" s="31">
         <f>SUM(J42:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="29">
+      <c r="K45" s="31">
         <f>SUM(K42:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="31">
         <f>SUM(L42:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="29">
+      <c r="M45" s="31">
         <f>SUM(M42:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="29">
+      <c r="N45" s="31">
         <f>SUM(N42:N44)</f>
         <v/>
       </c>
-      <c r="O45" s="29">
+      <c r="O45" s="31">
         <f>SUM(O42:O44)</f>
         <v/>
       </c>
-      <c r="P45" s="29">
+      <c r="P45" s="31">
         <f>SUM(P42:P44)</f>
         <v/>
       </c>
-      <c r="Q45" s="29">
+      <c r="Q45" s="31">
         <f>SUM(Q42:Q44)</f>
         <v/>
       </c>
-      <c r="R45" s="29">
+      <c r="R45" s="31">
         <f>SUM(R42:R44)</f>
         <v/>
       </c>
-      <c r="S45" s="29">
+      <c r="S45" s="31">
         <f>SUM(S42:S44)</f>
         <v/>
       </c>
-      <c r="T45" s="29">
+      <c r="T45" s="31">
         <f>SUM(T42:T44)</f>
         <v/>
       </c>
-      <c r="U45" s="29">
+      <c r="U45" s="31">
         <f>SUM(U42:U44)</f>
         <v/>
       </c>
-      <c r="V45" s="29">
+      <c r="V45" s="31">
         <f>SUM(V42:V44)</f>
         <v/>
       </c>
-      <c r="W45" s="29">
+      <c r="W45" s="31">
         <f>SUM(W42:W44)</f>
         <v/>
       </c>
-      <c r="X45" s="29">
+      <c r="X45" s="31">
         <f>SUM(X42:X44)</f>
         <v/>
       </c>
-      <c r="Y45" s="29">
+      <c r="Y45" s="31">
         <f>SUM(Y42:Y44)</f>
         <v/>
       </c>
-      <c r="Z45" s="29">
+      <c r="Z45" s="31">
         <f>SUM(Z42:Z44)</f>
         <v/>
       </c>
-      <c r="AA45" s="29">
+      <c r="AA45" s="31">
         <f>SUM(AA42:AA44)</f>
         <v/>
       </c>
@@ -3198,107 +3205,107 @@
           <t>財務収支 差額（収入－支出）</t>
         </is>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="32">
         <f>B41-B45</f>
         <v/>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="32">
         <f>C41-C45</f>
         <v/>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="32">
         <f>D41-D45</f>
         <v/>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="32">
         <f>E41-E45</f>
         <v/>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="32">
         <f>F41-F45</f>
         <v/>
       </c>
-      <c r="G46" s="30">
+      <c r="G46" s="32">
         <f>G41-G45</f>
         <v/>
       </c>
-      <c r="H46" s="30">
+      <c r="H46" s="32">
         <f>H41-H45</f>
         <v/>
       </c>
-      <c r="I46" s="30">
+      <c r="I46" s="32">
         <f>I41-I45</f>
         <v/>
       </c>
-      <c r="J46" s="30">
+      <c r="J46" s="32">
         <f>J41-J45</f>
         <v/>
       </c>
-      <c r="K46" s="30">
+      <c r="K46" s="32">
         <f>K41-K45</f>
         <v/>
       </c>
-      <c r="L46" s="30">
+      <c r="L46" s="32">
         <f>L41-L45</f>
         <v/>
       </c>
-      <c r="M46" s="30">
+      <c r="M46" s="32">
         <f>M41-M45</f>
         <v/>
       </c>
-      <c r="N46" s="30">
+      <c r="N46" s="32">
         <f>N41-N45</f>
         <v/>
       </c>
-      <c r="O46" s="30">
+      <c r="O46" s="32">
         <f>O41-O45</f>
         <v/>
       </c>
-      <c r="P46" s="30">
+      <c r="P46" s="32">
         <f>P41-P45</f>
         <v/>
       </c>
-      <c r="Q46" s="30">
+      <c r="Q46" s="32">
         <f>Q41-Q45</f>
         <v/>
       </c>
-      <c r="R46" s="30">
+      <c r="R46" s="32">
         <f>R41-R45</f>
         <v/>
       </c>
-      <c r="S46" s="30">
+      <c r="S46" s="32">
         <f>S41-S45</f>
         <v/>
       </c>
-      <c r="T46" s="30">
+      <c r="T46" s="32">
         <f>T41-T45</f>
         <v/>
       </c>
-      <c r="U46" s="30">
+      <c r="U46" s="32">
         <f>U41-U45</f>
         <v/>
       </c>
-      <c r="V46" s="30">
+      <c r="V46" s="32">
         <f>V41-V45</f>
         <v/>
       </c>
-      <c r="W46" s="30">
+      <c r="W46" s="32">
         <f>W41-W45</f>
         <v/>
       </c>
-      <c r="X46" s="30">
+      <c r="X46" s="32">
         <f>X41-X45</f>
         <v/>
       </c>
-      <c r="Y46" s="30">
+      <c r="Y46" s="32">
         <f>Y41-Y45</f>
         <v/>
       </c>
-      <c r="Z46" s="30">
+      <c r="Z46" s="32">
         <f>Z41-Z45</f>
         <v/>
       </c>
-      <c r="AA46" s="30">
+      <c r="AA46" s="32">
         <f>AA41-AA45</f>
         <v/>
       </c>
@@ -3309,106 +3316,106 @@
           <t>前月繰越（月初残高）</t>
         </is>
       </c>
-      <c r="B47" s="26" t="n">
+      <c r="B47" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="32">
         <f>B48</f>
         <v/>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="32">
         <f>C48</f>
         <v/>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="32">
         <f>D48</f>
         <v/>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="32">
         <f>E48</f>
         <v/>
       </c>
-      <c r="G47" s="30">
+      <c r="G47" s="32">
         <f>F48</f>
         <v/>
       </c>
-      <c r="H47" s="30">
+      <c r="H47" s="32">
         <f>G48</f>
         <v/>
       </c>
-      <c r="I47" s="30">
+      <c r="I47" s="32">
         <f>H48</f>
         <v/>
       </c>
-      <c r="J47" s="30">
+      <c r="J47" s="32">
         <f>I48</f>
         <v/>
       </c>
-      <c r="K47" s="30">
+      <c r="K47" s="32">
         <f>J48</f>
         <v/>
       </c>
-      <c r="L47" s="30">
+      <c r="L47" s="32">
         <f>K48</f>
         <v/>
       </c>
-      <c r="M47" s="30">
+      <c r="M47" s="32">
         <f>L48</f>
         <v/>
       </c>
-      <c r="N47" s="30">
+      <c r="N47" s="32">
         <f>M48</f>
         <v/>
       </c>
-      <c r="O47" s="30">
+      <c r="O47" s="32">
         <f>N48</f>
         <v/>
       </c>
-      <c r="P47" s="30">
+      <c r="P47" s="32">
         <f>O48</f>
         <v/>
       </c>
-      <c r="Q47" s="30">
+      <c r="Q47" s="32">
         <f>P48</f>
         <v/>
       </c>
-      <c r="R47" s="30">
+      <c r="R47" s="32">
         <f>Q48</f>
         <v/>
       </c>
-      <c r="S47" s="30">
+      <c r="S47" s="32">
         <f>R48</f>
         <v/>
       </c>
-      <c r="T47" s="30">
+      <c r="T47" s="32">
         <f>S48</f>
         <v/>
       </c>
-      <c r="U47" s="30">
+      <c r="U47" s="32">
         <f>T48</f>
         <v/>
       </c>
-      <c r="V47" s="30">
+      <c r="V47" s="32">
         <f>U48</f>
         <v/>
       </c>
-      <c r="W47" s="30">
+      <c r="W47" s="32">
         <f>V48</f>
         <v/>
       </c>
-      <c r="X47" s="30">
+      <c r="X47" s="32">
         <f>W48</f>
         <v/>
       </c>
-      <c r="Y47" s="30">
+      <c r="Y47" s="32">
         <f>X48</f>
         <v/>
       </c>
-      <c r="Z47" s="30">
+      <c r="Z47" s="32">
         <f>Y48</f>
         <v/>
       </c>
-      <c r="AA47" s="30">
+      <c r="AA47" s="32">
         <f>B47</f>
         <v/>
       </c>
@@ -3419,112 +3426,112 @@
           <t>翌月繰越（月末残高）</t>
         </is>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="32">
         <f>B47+B26+B36+B46</f>
         <v/>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="32">
         <f>C47+C26+C36+C46</f>
         <v/>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="32">
         <f>D47+D26+D36+D46</f>
         <v/>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="32">
         <f>E47+E26+E36+E46</f>
         <v/>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="32">
         <f>F47+F26+F36+F46</f>
         <v/>
       </c>
-      <c r="G48" s="30">
+      <c r="G48" s="32">
         <f>G47+G26+G36+G46</f>
         <v/>
       </c>
-      <c r="H48" s="30">
+      <c r="H48" s="32">
         <f>H47+H26+H36+H46</f>
         <v/>
       </c>
-      <c r="I48" s="30">
+      <c r="I48" s="32">
         <f>I47+I26+I36+I46</f>
         <v/>
       </c>
-      <c r="J48" s="30">
+      <c r="J48" s="32">
         <f>J47+J26+J36+J46</f>
         <v/>
       </c>
-      <c r="K48" s="30">
+      <c r="K48" s="32">
         <f>K47+K26+K36+K46</f>
         <v/>
       </c>
-      <c r="L48" s="30">
+      <c r="L48" s="32">
         <f>L47+L26+L36+L46</f>
         <v/>
       </c>
-      <c r="M48" s="30">
+      <c r="M48" s="32">
         <f>M47+M26+M36+M46</f>
         <v/>
       </c>
-      <c r="N48" s="30">
+      <c r="N48" s="32">
         <f>N47+N26+N36+N46</f>
         <v/>
       </c>
-      <c r="O48" s="30">
+      <c r="O48" s="32">
         <f>O47+O26+O36+O46</f>
         <v/>
       </c>
-      <c r="P48" s="30">
+      <c r="P48" s="32">
         <f>P47+P26+P36+P46</f>
         <v/>
       </c>
-      <c r="Q48" s="30">
+      <c r="Q48" s="32">
         <f>Q47+Q26+Q36+Q46</f>
         <v/>
       </c>
-      <c r="R48" s="30">
+      <c r="R48" s="32">
         <f>R47+R26+R36+R46</f>
         <v/>
       </c>
-      <c r="S48" s="30">
+      <c r="S48" s="32">
         <f>S47+S26+S36+S46</f>
         <v/>
       </c>
-      <c r="T48" s="30">
+      <c r="T48" s="32">
         <f>T47+T26+T36+T46</f>
         <v/>
       </c>
-      <c r="U48" s="30">
+      <c r="U48" s="32">
         <f>U47+U26+U36+U46</f>
         <v/>
       </c>
-      <c r="V48" s="30">
+      <c r="V48" s="32">
         <f>V47+V26+V36+V46</f>
         <v/>
       </c>
-      <c r="W48" s="30">
+      <c r="W48" s="32">
         <f>W47+W26+W36+W46</f>
         <v/>
       </c>
-      <c r="X48" s="30">
+      <c r="X48" s="32">
         <f>X47+X26+X36+X46</f>
         <v/>
       </c>
-      <c r="Y48" s="30">
+      <c r="Y48" s="32">
         <f>Y47+Y26+Y36+Y46</f>
         <v/>
       </c>
-      <c r="Z48" s="30">
+      <c r="Z48" s="32">
         <f>Z47+Z26+Z36+Z46</f>
         <v/>
       </c>
-      <c r="AA48" s="30">
+      <c r="AA48" s="32">
         <f>Z48</f>
         <v/>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>残高判定</t>
@@ -3704,103 +3711,103 @@
           <t xml:space="preserve">  本来の納付額（前月と同額を自動・変わる月だけ入力）</t>
         </is>
       </c>
-      <c r="B53" s="26" t="n">
+      <c r="B53" s="28" t="n">
         <v>1550000</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="33">
         <f>B53</f>
         <v/>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="33">
         <f>C53</f>
         <v/>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="33">
         <f>D53</f>
         <v/>
       </c>
-      <c r="F53" s="26" t="n">
+      <c r="F53" s="28" t="n">
         <v>1650000</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="33">
         <f>F53</f>
         <v/>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="33">
         <f>G53</f>
         <v/>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="33">
         <f>H53</f>
         <v/>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="33">
         <f>I53</f>
         <v/>
       </c>
-      <c r="K53" s="26" t="n">
+      <c r="K53" s="28" t="n">
         <v>1800000</v>
       </c>
-      <c r="L53" s="26" t="n">
+      <c r="L53" s="28" t="n">
         <v>1850000</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="33">
         <f>L53</f>
         <v/>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="33">
         <f>M53</f>
         <v/>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="33">
         <f>N53</f>
         <v/>
       </c>
-      <c r="P53" s="31">
+      <c r="P53" s="33">
         <f>O53</f>
         <v/>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="33">
         <f>P53</f>
         <v/>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="33">
         <f>Q53</f>
         <v/>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="33">
         <f>R53</f>
         <v/>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="33">
         <f>S53</f>
         <v/>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="33">
         <f>T53</f>
         <v/>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="33">
         <f>U53</f>
         <v/>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="33">
         <f>V53</f>
         <v/>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="33">
         <f>W53</f>
         <v/>
       </c>
-      <c r="Y53" s="31">
+      <c r="Y53" s="33">
         <f>X53</f>
         <v/>
       </c>
-      <c r="Z53" s="31">
+      <c r="Z53" s="33">
         <f>Y53</f>
         <v/>
       </c>
-      <c r="AA53" s="28">
+      <c r="AA53" s="30">
         <f>SUM(B53:Z53)</f>
         <v/>
       </c>
@@ -3811,107 +3818,107 @@
           <t xml:space="preserve">  実際の納付額（上段から自動）</t>
         </is>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="34">
         <f>B19</f>
         <v/>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="34">
         <f>C19</f>
         <v/>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="34">
         <f>D19</f>
         <v/>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="34">
         <f>E19</f>
         <v/>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="34">
         <f>F19</f>
         <v/>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="34">
         <f>G19</f>
         <v/>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="34">
         <f>H19</f>
         <v/>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="34">
         <f>I19</f>
         <v/>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="34">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="34">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L54" s="32">
+      <c r="L54" s="34">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M54" s="32">
+      <c r="M54" s="34">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N54" s="32">
+      <c r="N54" s="34">
         <f>N19</f>
         <v/>
       </c>
-      <c r="O54" s="32">
+      <c r="O54" s="34">
         <f>O19</f>
         <v/>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="34">
         <f>P19</f>
         <v/>
       </c>
-      <c r="Q54" s="32">
+      <c r="Q54" s="34">
         <f>Q19</f>
         <v/>
       </c>
-      <c r="R54" s="32">
+      <c r="R54" s="34">
         <f>R19</f>
         <v/>
       </c>
-      <c r="S54" s="32">
+      <c r="S54" s="34">
         <f>S19</f>
         <v/>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="34">
         <f>T19</f>
         <v/>
       </c>
-      <c r="U54" s="32">
+      <c r="U54" s="34">
         <f>U19</f>
         <v/>
       </c>
-      <c r="V54" s="32">
+      <c r="V54" s="34">
         <f>V19</f>
         <v/>
       </c>
-      <c r="W54" s="32">
+      <c r="W54" s="34">
         <f>W19</f>
         <v/>
       </c>
-      <c r="X54" s="32">
+      <c r="X54" s="34">
         <f>X19</f>
         <v/>
       </c>
-      <c r="Y54" s="32">
+      <c r="Y54" s="34">
         <f>Y19</f>
         <v/>
       </c>
-      <c r="Z54" s="32">
+      <c r="Z54" s="34">
         <f>Z19</f>
         <v/>
       </c>
-      <c r="AA54" s="28">
+      <c r="AA54" s="30">
         <f>SUM(B54:Z54)</f>
         <v/>
       </c>
@@ -3922,107 +3929,107 @@
           <t xml:space="preserve">  滞納残高（累計）</t>
         </is>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="31">
         <f>B53-B54</f>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="31">
         <f>B55+C53-C54</f>
         <v/>
       </c>
-      <c r="D55" s="29">
+      <c r="D55" s="31">
         <f>C55+D53-D54</f>
         <v/>
       </c>
-      <c r="E55" s="29">
+      <c r="E55" s="31">
         <f>D55+E53-E54</f>
         <v/>
       </c>
-      <c r="F55" s="29">
+      <c r="F55" s="31">
         <f>E55+F53-F54</f>
         <v/>
       </c>
-      <c r="G55" s="29">
+      <c r="G55" s="31">
         <f>F55+G53-G54</f>
         <v/>
       </c>
-      <c r="H55" s="29">
+      <c r="H55" s="31">
         <f>G55+H53-H54</f>
         <v/>
       </c>
-      <c r="I55" s="29">
+      <c r="I55" s="31">
         <f>H55+I53-I54</f>
         <v/>
       </c>
-      <c r="J55" s="29">
+      <c r="J55" s="31">
         <f>I55+J53-J54</f>
         <v/>
       </c>
-      <c r="K55" s="29">
+      <c r="K55" s="31">
         <f>J55+K53-K54</f>
         <v/>
       </c>
-      <c r="L55" s="29">
+      <c r="L55" s="31">
         <f>K55+L53-L54</f>
         <v/>
       </c>
-      <c r="M55" s="29">
+      <c r="M55" s="31">
         <f>L55+M53-M54</f>
         <v/>
       </c>
-      <c r="N55" s="29">
+      <c r="N55" s="31">
         <f>M55+N53-N54</f>
         <v/>
       </c>
-      <c r="O55" s="29">
+      <c r="O55" s="31">
         <f>N55+O53-O54</f>
         <v/>
       </c>
-      <c r="P55" s="29">
+      <c r="P55" s="31">
         <f>O55+P53-P54</f>
         <v/>
       </c>
-      <c r="Q55" s="29">
+      <c r="Q55" s="31">
         <f>P55+Q53-Q54</f>
         <v/>
       </c>
-      <c r="R55" s="29">
+      <c r="R55" s="31">
         <f>Q55+R53-R54</f>
         <v/>
       </c>
-      <c r="S55" s="29">
+      <c r="S55" s="31">
         <f>R55+S53-S54</f>
         <v/>
       </c>
-      <c r="T55" s="29">
+      <c r="T55" s="31">
         <f>S55+T53-T54</f>
         <v/>
       </c>
-      <c r="U55" s="29">
+      <c r="U55" s="31">
         <f>T55+U53-U54</f>
         <v/>
       </c>
-      <c r="V55" s="29">
+      <c r="V55" s="31">
         <f>U55+V53-V54</f>
         <v/>
       </c>
-      <c r="W55" s="29">
+      <c r="W55" s="31">
         <f>V55+W53-W54</f>
         <v/>
       </c>
-      <c r="X55" s="29">
+      <c r="X55" s="31">
         <f>W55+X53-X54</f>
         <v/>
       </c>
-      <c r="Y55" s="29">
+      <c r="Y55" s="31">
         <f>X55+Y53-Y54</f>
         <v/>
       </c>
-      <c r="Z55" s="29">
+      <c r="Z55" s="31">
         <f>Y55+Z53-Z54</f>
         <v/>
       </c>
-      <c r="AA55" s="29">
+      <c r="AA55" s="31">
         <f>Z55</f>
         <v/>
       </c>
@@ -4066,106 +4073,96 @@
           <t xml:space="preserve">  本来の納付額（前月と同額を自動・変わる月だけ入力）</t>
         </is>
       </c>
-      <c r="B57" s="26" t="n">
+      <c r="B57" s="33" t="n">
+        <v>335000</v>
+      </c>
+      <c r="C57" s="33" t="n">
+        <v>335000</v>
+      </c>
+      <c r="D57" s="33" t="n">
+        <v>335000</v>
+      </c>
+      <c r="E57" s="33" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F57" s="33" t="n">
+        <v>340000</v>
+      </c>
+      <c r="G57" s="33" t="n">
+        <v>340000</v>
+      </c>
+      <c r="H57" s="33" t="n">
+        <v>340000</v>
+      </c>
+      <c r="I57" s="33" t="n">
+        <v>340000</v>
+      </c>
+      <c r="J57" s="33" t="n">
+        <v>340000</v>
+      </c>
+      <c r="K57" s="33" t="n">
         <v>350000</v>
       </c>
-      <c r="C57" s="31">
-        <f>B57</f>
-        <v/>
-      </c>
-      <c r="D57" s="31">
-        <f>C57</f>
-        <v/>
-      </c>
-      <c r="E57" s="31">
-        <f>D57</f>
-        <v/>
-      </c>
-      <c r="F57" s="31">
-        <f>E57</f>
-        <v/>
-      </c>
-      <c r="G57" s="31">
-        <f>F57</f>
-        <v/>
-      </c>
-      <c r="H57" s="31">
-        <f>G57</f>
-        <v/>
-      </c>
-      <c r="I57" s="31">
-        <f>H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="31">
-        <f>I57</f>
-        <v/>
-      </c>
-      <c r="K57" s="31">
-        <f>J57</f>
-        <v/>
-      </c>
-      <c r="L57" s="31">
-        <f>K57</f>
-        <v/>
-      </c>
-      <c r="M57" s="31">
+      <c r="L57" s="33" t="n">
+        <v>350000</v>
+      </c>
+      <c r="M57" s="33">
         <f>L57</f>
         <v/>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="33">
         <f>M57</f>
         <v/>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="33">
         <f>N57</f>
         <v/>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="33">
         <f>O57</f>
         <v/>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="33">
         <f>P57</f>
         <v/>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="33">
         <f>Q57</f>
         <v/>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="33">
         <f>R57</f>
         <v/>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="33">
         <f>S57</f>
         <v/>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="33">
         <f>T57</f>
         <v/>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="33">
         <f>U57</f>
         <v/>
       </c>
-      <c r="W57" s="31">
+      <c r="W57" s="33">
         <f>V57</f>
         <v/>
       </c>
-      <c r="X57" s="31">
+      <c r="X57" s="33">
         <f>W57</f>
         <v/>
       </c>
-      <c r="Y57" s="31">
+      <c r="Y57" s="33">
         <f>X57</f>
         <v/>
       </c>
-      <c r="Z57" s="31">
+      <c r="Z57" s="33">
         <f>Y57</f>
         <v/>
       </c>
-      <c r="AA57" s="28">
+      <c r="AA57" s="30">
         <f>SUM(B57:Z57)</f>
         <v/>
       </c>
@@ -4176,107 +4173,107 @@
           <t xml:space="preserve">  実際の納付額（上段から自動）</t>
         </is>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="34">
         <f>B20</f>
         <v/>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="34">
         <f>C20</f>
         <v/>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="34">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="34">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F58" s="32">
+      <c r="F58" s="34">
         <f>F20</f>
         <v/>
       </c>
-      <c r="G58" s="32">
+      <c r="G58" s="34">
         <f>G20</f>
         <v/>
       </c>
-      <c r="H58" s="32">
+      <c r="H58" s="34">
         <f>H20</f>
         <v/>
       </c>
-      <c r="I58" s="32">
+      <c r="I58" s="34">
         <f>I20</f>
         <v/>
       </c>
-      <c r="J58" s="32">
+      <c r="J58" s="34">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K58" s="32">
+      <c r="K58" s="34">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L58" s="32">
+      <c r="L58" s="34">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M58" s="32">
+      <c r="M58" s="34">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N58" s="32">
+      <c r="N58" s="34">
         <f>N20</f>
         <v/>
       </c>
-      <c r="O58" s="32">
+      <c r="O58" s="34">
         <f>O20</f>
         <v/>
       </c>
-      <c r="P58" s="32">
+      <c r="P58" s="34">
         <f>P20</f>
         <v/>
       </c>
-      <c r="Q58" s="32">
+      <c r="Q58" s="34">
         <f>Q20</f>
         <v/>
       </c>
-      <c r="R58" s="32">
+      <c r="R58" s="34">
         <f>R20</f>
         <v/>
       </c>
-      <c r="S58" s="32">
+      <c r="S58" s="34">
         <f>S20</f>
         <v/>
       </c>
-      <c r="T58" s="32">
+      <c r="T58" s="34">
         <f>T20</f>
         <v/>
       </c>
-      <c r="U58" s="32">
+      <c r="U58" s="34">
         <f>U20</f>
         <v/>
       </c>
-      <c r="V58" s="32">
+      <c r="V58" s="34">
         <f>V20</f>
         <v/>
       </c>
-      <c r="W58" s="32">
+      <c r="W58" s="34">
         <f>W20</f>
         <v/>
       </c>
-      <c r="X58" s="32">
+      <c r="X58" s="34">
         <f>X20</f>
         <v/>
       </c>
-      <c r="Y58" s="32">
+      <c r="Y58" s="34">
         <f>Y20</f>
         <v/>
       </c>
-      <c r="Z58" s="32">
+      <c r="Z58" s="34">
         <f>Z20</f>
         <v/>
       </c>
-      <c r="AA58" s="28">
+      <c r="AA58" s="30">
         <f>SUM(B58:Z58)</f>
         <v/>
       </c>
@@ -4287,107 +4284,107 @@
           <t xml:space="preserve">  滞納残高（累計）</t>
         </is>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="31">
         <f>B57-B58</f>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="31">
         <f>B59+C57-C58</f>
         <v/>
       </c>
-      <c r="D59" s="29">
+      <c r="D59" s="31">
         <f>C59+D57-D58</f>
         <v/>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="31">
         <f>D59+E57-E58</f>
         <v/>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="31">
         <f>E59+F57-F58</f>
         <v/>
       </c>
-      <c r="G59" s="29">
+      <c r="G59" s="31">
         <f>F59+G57-G58</f>
         <v/>
       </c>
-      <c r="H59" s="29">
+      <c r="H59" s="31">
         <f>G59+H57-H58</f>
         <v/>
       </c>
-      <c r="I59" s="29">
+      <c r="I59" s="31">
         <f>H59+I57-I58</f>
         <v/>
       </c>
-      <c r="J59" s="29">
+      <c r="J59" s="31">
         <f>I59+J57-J58</f>
         <v/>
       </c>
-      <c r="K59" s="29">
+      <c r="K59" s="31">
         <f>J59+K57-K58</f>
         <v/>
       </c>
-      <c r="L59" s="29">
+      <c r="L59" s="31">
         <f>K59+L57-L58</f>
         <v/>
       </c>
-      <c r="M59" s="29">
+      <c r="M59" s="31">
         <f>L59+M57-M58</f>
         <v/>
       </c>
-      <c r="N59" s="29">
+      <c r="N59" s="31">
         <f>M59+N57-N58</f>
         <v/>
       </c>
-      <c r="O59" s="29">
+      <c r="O59" s="31">
         <f>N59+O57-O58</f>
         <v/>
       </c>
-      <c r="P59" s="29">
+      <c r="P59" s="31">
         <f>O59+P57-P58</f>
         <v/>
       </c>
-      <c r="Q59" s="29">
+      <c r="Q59" s="31">
         <f>P59+Q57-Q58</f>
         <v/>
       </c>
-      <c r="R59" s="29">
+      <c r="R59" s="31">
         <f>Q59+R57-R58</f>
         <v/>
       </c>
-      <c r="S59" s="29">
+      <c r="S59" s="31">
         <f>R59+S57-S58</f>
         <v/>
       </c>
-      <c r="T59" s="29">
+      <c r="T59" s="31">
         <f>S59+T57-T58</f>
         <v/>
       </c>
-      <c r="U59" s="29">
+      <c r="U59" s="31">
         <f>T59+U57-U58</f>
         <v/>
       </c>
-      <c r="V59" s="29">
+      <c r="V59" s="31">
         <f>U59+V57-V58</f>
         <v/>
       </c>
-      <c r="W59" s="29">
+      <c r="W59" s="31">
         <f>V59+W57-W58</f>
         <v/>
       </c>
-      <c r="X59" s="29">
+      <c r="X59" s="31">
         <f>W59+X57-X58</f>
         <v/>
       </c>
-      <c r="Y59" s="29">
+      <c r="Y59" s="31">
         <f>X59+Y57-Y58</f>
         <v/>
       </c>
-      <c r="Z59" s="29">
+      <c r="Z59" s="31">
         <f>Y59+Z57-Z58</f>
         <v/>
       </c>
-      <c r="AA59" s="29">
+      <c r="AA59" s="31">
         <f>Z59</f>
         <v/>
       </c>
@@ -4398,250 +4395,731 @@
           <t>滞納残高 合計</t>
         </is>
       </c>
-      <c r="B60" s="30">
+      <c r="B60" s="32">
         <f>B55+B59</f>
         <v/>
       </c>
-      <c r="C60" s="30">
+      <c r="C60" s="32">
         <f>C55+C59</f>
         <v/>
       </c>
-      <c r="D60" s="30">
+      <c r="D60" s="32">
         <f>D55+D59</f>
         <v/>
       </c>
-      <c r="E60" s="30">
+      <c r="E60" s="32">
         <f>E55+E59</f>
         <v/>
       </c>
-      <c r="F60" s="30">
+      <c r="F60" s="32">
         <f>F55+F59</f>
         <v/>
       </c>
-      <c r="G60" s="30">
+      <c r="G60" s="32">
         <f>G55+G59</f>
         <v/>
       </c>
-      <c r="H60" s="30">
+      <c r="H60" s="32">
         <f>H55+H59</f>
         <v/>
       </c>
-      <c r="I60" s="30">
+      <c r="I60" s="32">
         <f>I55+I59</f>
         <v/>
       </c>
-      <c r="J60" s="30">
+      <c r="J60" s="32">
         <f>J55+J59</f>
         <v/>
       </c>
-      <c r="K60" s="30">
+      <c r="K60" s="32">
         <f>K55+K59</f>
         <v/>
       </c>
-      <c r="L60" s="30">
+      <c r="L60" s="32">
         <f>L55+L59</f>
         <v/>
       </c>
-      <c r="M60" s="30">
+      <c r="M60" s="32">
         <f>M55+M59</f>
         <v/>
       </c>
-      <c r="N60" s="30">
+      <c r="N60" s="32">
         <f>N55+N59</f>
         <v/>
       </c>
-      <c r="O60" s="30">
+      <c r="O60" s="32">
         <f>O55+O59</f>
         <v/>
       </c>
-      <c r="P60" s="30">
+      <c r="P60" s="32">
         <f>P55+P59</f>
         <v/>
       </c>
-      <c r="Q60" s="30">
+      <c r="Q60" s="32">
         <f>Q55+Q59</f>
         <v/>
       </c>
-      <c r="R60" s="30">
+      <c r="R60" s="32">
         <f>R55+R59</f>
         <v/>
       </c>
-      <c r="S60" s="30">
+      <c r="S60" s="32">
         <f>S55+S59</f>
         <v/>
       </c>
-      <c r="T60" s="30">
+      <c r="T60" s="32">
         <f>T55+T59</f>
         <v/>
       </c>
-      <c r="U60" s="30">
+      <c r="U60" s="32">
         <f>U55+U59</f>
         <v/>
       </c>
-      <c r="V60" s="30">
+      <c r="V60" s="32">
         <f>V55+V59</f>
         <v/>
       </c>
-      <c r="W60" s="30">
+      <c r="W60" s="32">
         <f>W55+W59</f>
         <v/>
       </c>
-      <c r="X60" s="30">
+      <c r="X60" s="32">
         <f>X55+X59</f>
         <v/>
       </c>
-      <c r="Y60" s="30">
+      <c r="Y60" s="32">
         <f>Y55+Y59</f>
         <v/>
       </c>
-      <c r="Z60" s="30">
+      <c r="Z60" s="32">
         <f>Z55+Z59</f>
         <v/>
       </c>
-      <c r="AA60" s="30">
+      <c r="AA60" s="32">
         <f>AA55+AA59</f>
         <v/>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="17" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
           <t>実質残高（月末残高－滞納残高合計）</t>
         </is>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="32">
         <f>B48-B60</f>
         <v/>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="32">
         <f>C48-C60</f>
         <v/>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="32">
         <f>D48-D60</f>
         <v/>
       </c>
-      <c r="E61" s="30">
+      <c r="E61" s="32">
         <f>E48-E60</f>
         <v/>
       </c>
-      <c r="F61" s="30">
+      <c r="F61" s="32">
         <f>F48-F60</f>
         <v/>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="32">
         <f>G48-G60</f>
         <v/>
       </c>
-      <c r="H61" s="30">
+      <c r="H61" s="32">
         <f>H48-H60</f>
         <v/>
       </c>
-      <c r="I61" s="30">
+      <c r="I61" s="32">
         <f>I48-I60</f>
         <v/>
       </c>
-      <c r="J61" s="30">
+      <c r="J61" s="32">
         <f>J48-J60</f>
         <v/>
       </c>
-      <c r="K61" s="30">
+      <c r="K61" s="32">
         <f>K48-K60</f>
         <v/>
       </c>
-      <c r="L61" s="30">
+      <c r="L61" s="32">
         <f>L48-L60</f>
         <v/>
       </c>
-      <c r="M61" s="30">
+      <c r="M61" s="32">
         <f>M48-M60</f>
         <v/>
       </c>
-      <c r="N61" s="30">
+      <c r="N61" s="32">
         <f>N48-N60</f>
         <v/>
       </c>
-      <c r="O61" s="30">
+      <c r="O61" s="32">
         <f>O48-O60</f>
         <v/>
       </c>
-      <c r="P61" s="30">
+      <c r="P61" s="32">
         <f>P48-P60</f>
         <v/>
       </c>
-      <c r="Q61" s="30">
+      <c r="Q61" s="32">
         <f>Q48-Q60</f>
         <v/>
       </c>
-      <c r="R61" s="30">
+      <c r="R61" s="32">
         <f>R48-R60</f>
         <v/>
       </c>
-      <c r="S61" s="30">
+      <c r="S61" s="32">
         <f>S48-S60</f>
         <v/>
       </c>
-      <c r="T61" s="30">
+      <c r="T61" s="32">
         <f>T48-T60</f>
         <v/>
       </c>
-      <c r="U61" s="30">
+      <c r="U61" s="32">
         <f>U48-U60</f>
         <v/>
       </c>
-      <c r="V61" s="30">
+      <c r="V61" s="32">
         <f>V48-V60</f>
         <v/>
       </c>
-      <c r="W61" s="30">
+      <c r="W61" s="32">
         <f>W48-W60</f>
         <v/>
       </c>
-      <c r="X61" s="30">
+      <c r="X61" s="32">
         <f>X48-X60</f>
         <v/>
       </c>
-      <c r="Y61" s="30">
+      <c r="Y61" s="32">
         <f>Y48-Y60</f>
         <v/>
       </c>
-      <c r="Z61" s="30">
+      <c r="Z61" s="32">
         <f>Z48-Z60</f>
         <v/>
       </c>
-      <c r="AA61" s="30">
+      <c r="AA61" s="32">
         <f>AA48-AA60</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1"/>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>借入金残高管理 ※上段の財務収支（借入金・借入金返済）から自動</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="22" t="n"/>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="22" t="n"/>
+      <c r="J63" s="22" t="n"/>
+      <c r="K63" s="22" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
+      <c r="O63" s="22" t="n"/>
+      <c r="P63" s="22" t="n"/>
+      <c r="Q63" s="22" t="n"/>
+      <c r="R63" s="22" t="n"/>
+      <c r="S63" s="22" t="n"/>
+      <c r="T63" s="22" t="n"/>
+      <c r="U63" s="22" t="n"/>
+      <c r="V63" s="22" t="n"/>
+      <c r="W63" s="22" t="n"/>
+      <c r="X63" s="22" t="n"/>
+      <c r="Y63" s="22" t="n"/>
+      <c r="Z63" s="22" t="n"/>
+      <c r="AA63" s="22" t="n"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>前月末 借入金残高</t>
+        </is>
+      </c>
+      <c r="B64" s="28" t="n"/>
+      <c r="C64" s="31">
+        <f>B67</f>
+        <v/>
+      </c>
+      <c r="D64" s="31">
+        <f>C67</f>
+        <v/>
+      </c>
+      <c r="E64" s="31">
+        <f>D67</f>
+        <v/>
+      </c>
+      <c r="F64" s="31">
+        <f>E67</f>
+        <v/>
+      </c>
+      <c r="G64" s="31">
+        <f>F67</f>
+        <v/>
+      </c>
+      <c r="H64" s="31">
+        <f>G67</f>
+        <v/>
+      </c>
+      <c r="I64" s="31">
+        <f>H67</f>
+        <v/>
+      </c>
+      <c r="J64" s="31">
+        <f>I67</f>
+        <v/>
+      </c>
+      <c r="K64" s="31">
+        <f>J67</f>
+        <v/>
+      </c>
+      <c r="L64" s="31">
+        <f>K67</f>
+        <v/>
+      </c>
+      <c r="M64" s="31">
+        <f>L67</f>
+        <v/>
+      </c>
+      <c r="N64" s="31">
+        <f>M67</f>
+        <v/>
+      </c>
+      <c r="O64" s="31">
+        <f>N67</f>
+        <v/>
+      </c>
+      <c r="P64" s="31">
+        <f>O67</f>
+        <v/>
+      </c>
+      <c r="Q64" s="31">
+        <f>P67</f>
+        <v/>
+      </c>
+      <c r="R64" s="31">
+        <f>Q67</f>
+        <v/>
+      </c>
+      <c r="S64" s="31">
+        <f>R67</f>
+        <v/>
+      </c>
+      <c r="T64" s="31">
+        <f>S67</f>
+        <v/>
+      </c>
+      <c r="U64" s="31">
+        <f>T67</f>
+        <v/>
+      </c>
+      <c r="V64" s="31">
+        <f>U67</f>
+        <v/>
+      </c>
+      <c r="W64" s="31">
+        <f>V67</f>
+        <v/>
+      </c>
+      <c r="X64" s="31">
+        <f>W67</f>
+        <v/>
+      </c>
+      <c r="Y64" s="31">
+        <f>X67</f>
+        <v/>
+      </c>
+      <c r="Z64" s="31">
+        <f>Y67</f>
+        <v/>
+      </c>
+      <c r="AA64" s="30">
+        <f>B64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  借入（上段から自動）</t>
+        </is>
+      </c>
+      <c r="B65" s="34">
+        <f>B38</f>
+        <v/>
+      </c>
+      <c r="C65" s="34">
+        <f>C38</f>
+        <v/>
+      </c>
+      <c r="D65" s="34">
+        <f>D38</f>
+        <v/>
+      </c>
+      <c r="E65" s="34">
+        <f>E38</f>
+        <v/>
+      </c>
+      <c r="F65" s="34">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="G65" s="34">
+        <f>G38</f>
+        <v/>
+      </c>
+      <c r="H65" s="34">
+        <f>H38</f>
+        <v/>
+      </c>
+      <c r="I65" s="34">
+        <f>I38</f>
+        <v/>
+      </c>
+      <c r="J65" s="34">
+        <f>J38</f>
+        <v/>
+      </c>
+      <c r="K65" s="34">
+        <f>K38</f>
+        <v/>
+      </c>
+      <c r="L65" s="34">
+        <f>L38</f>
+        <v/>
+      </c>
+      <c r="M65" s="34">
+        <f>M38</f>
+        <v/>
+      </c>
+      <c r="N65" s="34">
+        <f>N38</f>
+        <v/>
+      </c>
+      <c r="O65" s="34">
+        <f>O38</f>
+        <v/>
+      </c>
+      <c r="P65" s="34">
+        <f>P38</f>
+        <v/>
+      </c>
+      <c r="Q65" s="34">
+        <f>Q38</f>
+        <v/>
+      </c>
+      <c r="R65" s="34">
+        <f>R38</f>
+        <v/>
+      </c>
+      <c r="S65" s="34">
+        <f>S38</f>
+        <v/>
+      </c>
+      <c r="T65" s="34">
+        <f>T38</f>
+        <v/>
+      </c>
+      <c r="U65" s="34">
+        <f>U38</f>
+        <v/>
+      </c>
+      <c r="V65" s="34">
+        <f>V38</f>
+        <v/>
+      </c>
+      <c r="W65" s="34">
+        <f>W38</f>
+        <v/>
+      </c>
+      <c r="X65" s="34">
+        <f>X38</f>
+        <v/>
+      </c>
+      <c r="Y65" s="34">
+        <f>Y38</f>
+        <v/>
+      </c>
+      <c r="Z65" s="34">
+        <f>Z38</f>
+        <v/>
+      </c>
+      <c r="AA65" s="30">
+        <f>SUM(B65:Z65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  返済（上段から自動）</t>
+        </is>
+      </c>
+      <c r="B66" s="34">
+        <f>B42</f>
+        <v/>
+      </c>
+      <c r="C66" s="34">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="D66" s="34">
+        <f>D42</f>
+        <v/>
+      </c>
+      <c r="E66" s="34">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="F66" s="34">
+        <f>F42</f>
+        <v/>
+      </c>
+      <c r="G66" s="34">
+        <f>G42</f>
+        <v/>
+      </c>
+      <c r="H66" s="34">
+        <f>H42</f>
+        <v/>
+      </c>
+      <c r="I66" s="34">
+        <f>I42</f>
+        <v/>
+      </c>
+      <c r="J66" s="34">
+        <f>J42</f>
+        <v/>
+      </c>
+      <c r="K66" s="34">
+        <f>K42</f>
+        <v/>
+      </c>
+      <c r="L66" s="34">
+        <f>L42</f>
+        <v/>
+      </c>
+      <c r="M66" s="34">
+        <f>M42</f>
+        <v/>
+      </c>
+      <c r="N66" s="34">
+        <f>N42</f>
+        <v/>
+      </c>
+      <c r="O66" s="34">
+        <f>O42</f>
+        <v/>
+      </c>
+      <c r="P66" s="34">
+        <f>P42</f>
+        <v/>
+      </c>
+      <c r="Q66" s="34">
+        <f>Q42</f>
+        <v/>
+      </c>
+      <c r="R66" s="34">
+        <f>R42</f>
+        <v/>
+      </c>
+      <c r="S66" s="34">
+        <f>S42</f>
+        <v/>
+      </c>
+      <c r="T66" s="34">
+        <f>T42</f>
+        <v/>
+      </c>
+      <c r="U66" s="34">
+        <f>U42</f>
+        <v/>
+      </c>
+      <c r="V66" s="34">
+        <f>V42</f>
+        <v/>
+      </c>
+      <c r="W66" s="34">
+        <f>W42</f>
+        <v/>
+      </c>
+      <c r="X66" s="34">
+        <f>X42</f>
+        <v/>
+      </c>
+      <c r="Y66" s="34">
+        <f>Y42</f>
+        <v/>
+      </c>
+      <c r="Z66" s="34">
+        <f>Z42</f>
+        <v/>
+      </c>
+      <c r="AA66" s="30">
+        <f>SUM(B66:Z66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>月末 借入金残高</t>
+        </is>
+      </c>
+      <c r="B67" s="31">
+        <f>B64+B65-B66</f>
+        <v/>
+      </c>
+      <c r="C67" s="31">
+        <f>C64+C65-C66</f>
+        <v/>
+      </c>
+      <c r="D67" s="31">
+        <f>D64+D65-D66</f>
+        <v/>
+      </c>
+      <c r="E67" s="31">
+        <f>E64+E65-E66</f>
+        <v/>
+      </c>
+      <c r="F67" s="31">
+        <f>F64+F65-F66</f>
+        <v/>
+      </c>
+      <c r="G67" s="31">
+        <f>G64+G65-G66</f>
+        <v/>
+      </c>
+      <c r="H67" s="31">
+        <f>H64+H65-H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="31">
+        <f>I64+I65-I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="31">
+        <f>J64+J65-J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="31">
+        <f>K64+K65-K66</f>
+        <v/>
+      </c>
+      <c r="L67" s="31">
+        <f>L64+L65-L66</f>
+        <v/>
+      </c>
+      <c r="M67" s="31">
+        <f>M64+M65-M66</f>
+        <v/>
+      </c>
+      <c r="N67" s="31">
+        <f>N64+N65-N66</f>
+        <v/>
+      </c>
+      <c r="O67" s="31">
+        <f>O64+O65-O66</f>
+        <v/>
+      </c>
+      <c r="P67" s="31">
+        <f>P64+P65-P66</f>
+        <v/>
+      </c>
+      <c r="Q67" s="31">
+        <f>Q64+Q65-Q66</f>
+        <v/>
+      </c>
+      <c r="R67" s="31">
+        <f>R64+R65-R66</f>
+        <v/>
+      </c>
+      <c r="S67" s="31">
+        <f>S64+S65-S66</f>
+        <v/>
+      </c>
+      <c r="T67" s="31">
+        <f>T64+T65-T66</f>
+        <v/>
+      </c>
+      <c r="U67" s="31">
+        <f>U64+U65-U66</f>
+        <v/>
+      </c>
+      <c r="V67" s="31">
+        <f>V64+V65-V66</f>
+        <v/>
+      </c>
+      <c r="W67" s="31">
+        <f>W64+W65-W66</f>
+        <v/>
+      </c>
+      <c r="X67" s="31">
+        <f>X64+X65-X66</f>
+        <v/>
+      </c>
+      <c r="Y67" s="31">
+        <f>Y64+Y65-Y66</f>
+        <v/>
+      </c>
+      <c r="Z67" s="31">
+        <f>Z64+Z65-Z66</f>
+        <v/>
+      </c>
+      <c r="AA67" s="31">
+        <f>Z67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>※滞納管理：上段の「法定福利費」「住民税その他税」に実際に払った額（満額でなくても）を入れると、下段の実際の納付額・滞納残高に自動反映。本来の納付額は前月と同額が自動で入ります（変わる月だけ上書き）。</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>※営業収入の2025年10月〜2026年8月は実績値（各セルのコメントに出典）。2026年9月は集計ファイル未確認のため空欄。</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>※借入金残高：B64 に期首の借入金残高を入れれば、上段「収入｜借入金」「支出｜借入金返済」から毎月の残高を自動計算（マイナスは赤表示＝入力の誤り）。利息は「支払利息・割引料」へ。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B48:Z49">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>B$48&lt;$B$4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B55:Z55">
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="2">
       <formula>B$55&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59:Z59">
-    <cfRule type="expression" priority="5" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="2">
       <formula>B$59&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4650,14 +5128,14 @@
       <formula>B$60&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:Z49">
-    <cfRule type="expression" priority="6" dxfId="0">
-      <formula>B$48&lt;$B$4</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B61:Z61">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>B$61&lt;$B$4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67:Z67">
+    <cfRule type="expression" priority="6" dxfId="5">
+      <formula>B$67&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
